--- a/outputs/SA_mlf.xlsx
+++ b/outputs/SA_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -991,12 +991,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>80.5</v>
+        <v>39</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>0.9352</v>
@@ -1125,12 +1125,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>39</v>
+        <v>80.5</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>0.9352</v>
@@ -1259,12 +1259,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HDWF2</t>
+          <t>HDWF1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 2</t>
+          <t>Hornsdale Wind Farm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1275,9 +1275,11 @@
       <c r="D12" s="4" t="n">
         <v>102.4</v>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
       <c r="F12" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0.9799</v>
@@ -1324,12 +1326,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HDWF1</t>
+          <t>HDWF3</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm</t>
+          <t>Hornsdale Wind Farm 3</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1338,14 +1340,10 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.9965000000000001</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -1391,12 +1389,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HDWF3</t>
+          <t>HDWF2</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 3</t>
+          <t>Hornsdale Wind Farm 2</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1405,10 +1403,12 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>112</v>
+        <v>102.4</v>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>0.9918</v>
+      </c>
       <c r="G14" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -1645,7 +1645,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1712,7 +1712,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2108,21 +2108,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Hallett 1 Wind Farm</t>
+          <t>Hallett Power Station</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>94.5</v>
+        <v>217</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0.9835</v>
@@ -2175,21 +2175,21 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Hallett Power Station</t>
+          <t>Hallett 1 Wind Farm</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>217</v>
+        <v>94.5</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9835</v>
@@ -2745,12 +2745,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Stage 2 North</t>
+          <t>Snowtown South Wind Farm</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>0.9782</v>
@@ -2812,12 +2812,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Snowtown South Wind Farm</t>
+          <t>Snowtown Wind Farm Stage 2 North</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>0.9782</v>
@@ -3485,7 +3485,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3750,17 +3750,13 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Tailem Bend 3 BESS</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>263</v>
-      </c>
+          <t>TB3BESS</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D52" s="3" t="inlineStr"/>
       <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
@@ -3855,7 +3851,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3922,7 +3918,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3936,7 +3932,7 @@
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0.9932</v>
@@ -3989,7 +3985,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4003,7 +3999,7 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>0.9932</v>
@@ -4056,7 +4052,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4070,7 +4066,7 @@
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0.9932</v>
@@ -4190,22 +4186,18 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
+          <t>SMFBESS2</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 1</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>153.65</v>
-      </c>
+          <t>SMFBESS2</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
@@ -4245,22 +4237,18 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
+          <t>SMFBESS1</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 2</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>153.65</v>
-      </c>
+          <t>SMFBESS1</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
@@ -4351,7 +4339,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4361,11 +4349,11 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="5" t="inlineStr"/>
@@ -4374,37 +4362,43 @@
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr"/>
-      <c r="L62" s="5" t="n">
-        <v>0.9966</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr"/>
       <c r="N62" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="O62" s="5" t="inlineStr"/>
+      <c r="O62" s="5" t="n">
+        <v>1.0102</v>
+      </c>
       <c r="P62" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="Q62" s="5" t="inlineStr"/>
+      <c r="Q62" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="R62" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="S62" s="5" t="inlineStr"/>
+      <c r="S62" s="5" t="n">
+        <v>0.9968</v>
+      </c>
       <c r="T62" s="5" t="n">
         <v>0.0023</v>
       </c>
       <c r="U62" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="V62" s="5" t="inlineStr"/>
-      <c r="W62" s="6" t="inlineStr"/>
+      <c r="V62" s="5" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="W62" s="6" t="n">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4414,11 +4408,11 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="5" t="inlineStr"/>
@@ -4427,38 +4421,32 @@
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
       <c r="K63" s="5" t="inlineStr"/>
-      <c r="L63" s="5" t="inlineStr"/>
-      <c r="M63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="n">
+        <v>0.9966</v>
+      </c>
+      <c r="M63" s="5" t="n">
+        <v>1.0079</v>
+      </c>
       <c r="N63" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="O63" s="5" t="n">
-        <v>1.0102</v>
-      </c>
+      <c r="O63" s="5" t="inlineStr"/>
       <c r="P63" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="Q63" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+      <c r="Q63" s="5" t="inlineStr"/>
       <c r="R63" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="S63" s="5" t="n">
-        <v>0.9968</v>
-      </c>
+      <c r="S63" s="5" t="inlineStr"/>
       <c r="T63" s="5" t="n">
         <v>0.0023</v>
       </c>
       <c r="U63" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="V63" s="5" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="W63" s="6" t="n">
-        <v>0.23</v>
-      </c>
+      <c r="V63" s="5" t="inlineStr"/>
+      <c r="W63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -4524,7 +4512,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT1</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4591,7 +4579,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4658,7 +4646,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT1</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5049,7 +5037,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>TORRENS ISLAND POWER STATION</t>
+          <t>Torrens Island Power Station</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -5292,47 +5280,51 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>BARKIPS1</t>
+          <t>DG_SA1</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Barker Inlet Power Station</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+          <t>SA1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr"/>
       <c r="D77" s="4" t="n">
-        <v>211</v>
-      </c>
-      <c r="E77" s="5" t="inlineStr"/>
-      <c r="F77" s="5" t="inlineStr"/>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I77" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="O77" s="5" t="inlineStr"/>
       <c r="P77" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="Q77" s="5" t="inlineStr"/>
       <c r="R77" s="5" t="n">
@@ -5340,10 +5332,10 @@
       </c>
       <c r="S77" s="5" t="inlineStr"/>
       <c r="T77" s="5" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="U77" s="6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="V77" s="5" t="inlineStr"/>
       <c r="W77" s="6" t="inlineStr"/>
@@ -5351,12 +5343,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>TORNL1</t>
+          <t>BARKIPS1</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>TORRENS ISLAND POWER STATION</t>
+          <t>Barker Inlet Power Station</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5365,41 +5357,33 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="M78" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="O78" s="5" t="inlineStr"/>
       <c r="P78" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="Q78" s="5" t="inlineStr"/>
       <c r="R78" s="5" t="n">
@@ -5407,10 +5391,10 @@
       </c>
       <c r="S78" s="5" t="inlineStr"/>
       <c r="T78" s="5" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="U78" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="V78" s="5" t="inlineStr"/>
       <c r="W78" s="6" t="inlineStr"/>
@@ -5418,17 +5402,21 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
+          <t>TORNL1</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>SA1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr"/>
+          <t>TORRENS ISLAND POWER STATION</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D79" s="4" t="n">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="E79" s="5" t="n">
         <v>1</v>
@@ -5481,7 +5469,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1</t>
+          <t>BOLIVAR1</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -5491,56 +5479,64 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr"/>
-      <c r="J80" s="5" t="inlineStr"/>
-      <c r="K80" s="5" t="inlineStr"/>
-      <c r="L80" s="5" t="inlineStr"/>
-      <c r="M80" s="5" t="inlineStr"/>
+        <v>9.9</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>1.0012</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>1.0011</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
       <c r="N80" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="O80" s="5" t="n">
-        <v>1.0004</v>
-      </c>
+      <c r="O80" s="5" t="inlineStr"/>
       <c r="P80" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="Q80" s="5" t="n">
-        <v>0.9999</v>
-      </c>
+      <c r="Q80" s="5" t="inlineStr"/>
       <c r="R80" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="S80" s="5" t="n">
-        <v>1.0002</v>
-      </c>
+      <c r="S80" s="5" t="inlineStr"/>
       <c r="T80" s="5" t="n">
         <v>0.0003</v>
       </c>
       <c r="U80" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V80" s="5" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="W80" s="6" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="V80" s="5" t="inlineStr"/>
+      <c r="W80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
+          <t>BOWWPV1</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5550,30 +5546,18 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>1.0012</v>
-      </c>
+        <v>8.25</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr"/>
       <c r="K81" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -5662,7 +5646,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>BOWWPV1</t>
+          <t>BOWWBA1</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5672,11 +5656,11 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>8.25</v>
+        <v>3</v>
       </c>
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="5" t="inlineStr"/>
@@ -5684,35 +5668,39 @@
       <c r="H83" s="5" t="inlineStr"/>
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr"/>
-      <c r="K83" s="5" t="n">
-        <v>1.0011</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
+      <c r="K83" s="5" t="inlineStr"/>
+      <c r="L83" s="5" t="inlineStr"/>
+      <c r="M83" s="5" t="inlineStr"/>
       <c r="N83" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="O83" s="5" t="inlineStr"/>
+      <c r="O83" s="5" t="n">
+        <v>1.0004</v>
+      </c>
       <c r="P83" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="Q83" s="5" t="inlineStr"/>
+      <c r="Q83" s="5" t="n">
+        <v>0.9999</v>
+      </c>
       <c r="R83" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="S83" s="5" t="inlineStr"/>
+      <c r="S83" s="5" t="n">
+        <v>1.0002</v>
+      </c>
       <c r="T83" s="5" t="n">
         <v>0.0003</v>
       </c>
       <c r="U83" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V83" s="5" t="inlineStr"/>
-      <c r="W83" s="6" t="inlineStr"/>
+      <c r="V83" s="5" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="W83" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -5784,22 +5772,18 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>WINGF1_1</t>
+          <t>DRYCNL</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Wingfield 1 Landfill Gas Power Station</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>Other Renewable</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>4.12</v>
-      </c>
+          <t>Dry Creek Gas Turbine Station</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
       <c r="E85" s="5" t="n">
         <v>1.0029</v>
       </c>
@@ -5851,18 +5835,22 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>DRYCNL</t>
+          <t>WINGF1_1</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Dry Creek Gas Turbine Station</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D86" s="3" t="inlineStr"/>
+          <t>Wingfield 1 Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>4.12</v>
+      </c>
       <c r="E86" s="5" t="n">
         <v>1.0029</v>
       </c>
@@ -6077,7 +6065,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1</t>
+          <t>HVWWPV1</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -6087,11 +6075,11 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E90" s="5" t="inlineStr"/>
       <c r="F90" s="5" t="inlineStr"/>
@@ -6099,44 +6087,40 @@
       <c r="H90" s="5" t="inlineStr"/>
       <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="5" t="inlineStr"/>
-      <c r="K90" s="5" t="inlineStr"/>
-      <c r="L90" s="5" t="inlineStr"/>
-      <c r="M90" s="5" t="inlineStr"/>
+      <c r="K90" s="5" t="n">
+        <v>1.0052</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>1.0041</v>
+      </c>
       <c r="N90" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="O90" s="5" t="n">
-        <v>1.0043</v>
-      </c>
+      <c r="O90" s="5" t="inlineStr"/>
       <c r="P90" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="Q90" s="5" t="n">
-        <v>1.0024</v>
-      </c>
+      <c r="Q90" s="5" t="inlineStr"/>
       <c r="R90" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="S90" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="S90" s="5" t="inlineStr"/>
       <c r="T90" s="5" t="n">
         <v>-0.0002</v>
       </c>
       <c r="U90" s="6" t="n">
         <v>-0.02</v>
       </c>
-      <c r="V90" s="5" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="W90" s="6" t="n">
-        <v>-0.02</v>
-      </c>
+      <c r="V90" s="5" t="inlineStr"/>
+      <c r="W90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>HVWWPV1</t>
+          <t>HVWWBA1</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -6146,11 +6130,11 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="5" t="inlineStr"/>
@@ -6158,35 +6142,39 @@
       <c r="H91" s="5" t="inlineStr"/>
       <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr"/>
-      <c r="K91" s="5" t="n">
-        <v>1.0052</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="M91" s="5" t="n">
-        <v>1.0041</v>
-      </c>
+      <c r="K91" s="5" t="inlineStr"/>
+      <c r="L91" s="5" t="inlineStr"/>
+      <c r="M91" s="5" t="inlineStr"/>
       <c r="N91" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="O91" s="5" t="inlineStr"/>
+      <c r="O91" s="5" t="n">
+        <v>1.0043</v>
+      </c>
       <c r="P91" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="Q91" s="5" t="inlineStr"/>
+      <c r="Q91" s="5" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="R91" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="S91" s="5" t="inlineStr"/>
+      <c r="S91" s="5" t="n">
+        <v>1.0022</v>
+      </c>
       <c r="T91" s="5" t="n">
         <v>-0.0002</v>
       </c>
       <c r="U91" s="6" t="n">
         <v>-0.02</v>
       </c>
-      <c r="V91" s="5" t="inlineStr"/>
-      <c r="W91" s="6" t="inlineStr"/>
+      <c r="V91" s="5" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="W91" s="6" t="n">
+        <v>-0.02</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -6258,39 +6246,29 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
+          <t>ADPPV1</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>1.0053</v>
-      </c>
+        <v>24.75</v>
+      </c>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr"/>
+      <c r="H93" s="5" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="5" t="n">
-        <v>1.005</v>
+        <v>1.0038</v>
       </c>
       <c r="K93" s="5" t="n">
         <v>1.0055</v>
@@ -6325,74 +6303,66 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
+          <t>ADPBA1</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Starfish Hill Wind Farm</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="M94" s="5" t="n">
-        <v>1.0039</v>
-      </c>
+        <v>7.76</v>
+      </c>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="5" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr"/>
+      <c r="J94" s="5" t="inlineStr"/>
+      <c r="K94" s="5" t="inlineStr"/>
+      <c r="L94" s="5" t="inlineStr"/>
+      <c r="M94" s="5" t="inlineStr"/>
       <c r="N94" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O94" s="5" t="inlineStr"/>
+      <c r="O94" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="P94" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q94" s="5" t="inlineStr"/>
+      <c r="Q94" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="R94" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S94" s="5" t="inlineStr"/>
+      <c r="S94" s="5" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="T94" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U94" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V94" s="5" t="inlineStr"/>
-      <c r="W94" s="6" t="inlineStr"/>
+      <c r="V94" s="5" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="W94" s="6" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
+          <t>ADPPV3</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -6406,7 +6376,7 @@
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="5" t="inlineStr"/>
@@ -6447,40 +6417,28 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
+          <t>ADPPV2</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Lonsdale Power Station</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>1.005</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="E96" s="5" t="inlineStr"/>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="5" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="5" t="inlineStr"/>
       <c r="K96" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -6514,28 +6472,40 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
+          <t>STARHLWF</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Starfish Hill Wind Farm</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="5" t="inlineStr"/>
+        <v>34.5</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>1.005</v>
+      </c>
       <c r="K97" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -6569,7 +6539,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
+          <t>CBWWPV1</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -6583,7 +6553,7 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>1.08</v>
+        <v>2.75</v>
       </c>
       <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="5" t="inlineStr"/>
@@ -6622,7 +6592,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
+          <t>CBWWDG2</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -6632,11 +6602,11 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>2.75</v>
+        <v>0.72</v>
       </c>
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="5" t="inlineStr"/>
@@ -6675,33 +6645,29 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>ADPPV1</t>
+          <t>CBWWDG1</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>24.75</v>
+        <v>2</v>
       </c>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr"/>
-      <c r="J100" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="J100" s="5" t="inlineStr"/>
+      <c r="K100" s="5" t="inlineStr"/>
       <c r="L100" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6732,21 +6698,21 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
+          <t>CBWWBG1</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>7.76</v>
+        <v>0.664</v>
       </c>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr"/>
@@ -6755,57 +6721,51 @@
       <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="5" t="inlineStr"/>
       <c r="K101" s="5" t="inlineStr"/>
-      <c r="L101" s="5" t="inlineStr"/>
-      <c r="M101" s="5" t="inlineStr"/>
+      <c r="L101" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="N101" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O101" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="O101" s="5" t="inlineStr"/>
       <c r="P101" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q101" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="Q101" s="5" t="inlineStr"/>
       <c r="R101" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S101" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="S101" s="5" t="inlineStr"/>
       <c r="T101" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U101" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V101" s="5" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="W101" s="6" t="n">
-        <v>-0.04</v>
-      </c>
+      <c r="V101" s="5" t="inlineStr"/>
+      <c r="W101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>ADPMH1</t>
+          <t>CBWWBA1</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="5" t="inlineStr"/>
@@ -6813,40 +6773,44 @@
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr"/>
-      <c r="K102" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="L102" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="M102" s="5" t="n">
-        <v>1.0039</v>
-      </c>
+      <c r="K102" s="5" t="inlineStr"/>
+      <c r="L102" s="5" t="inlineStr"/>
+      <c r="M102" s="5" t="inlineStr"/>
       <c r="N102" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O102" s="5" t="inlineStr"/>
+      <c r="O102" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="P102" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q102" s="5" t="inlineStr"/>
+      <c r="Q102" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="R102" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S102" s="5" t="inlineStr"/>
+      <c r="S102" s="5" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="T102" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U102" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V102" s="5" t="inlineStr"/>
-      <c r="W102" s="6" t="inlineStr"/>
+      <c r="V102" s="5" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="W102" s="6" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG1</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -6856,11 +6820,11 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="5" t="inlineStr"/>
@@ -6899,29 +6863,43 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
+          <t>PTSTAN1</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Pt Stanvac Power Station</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr"/>
-      <c r="J104" s="5" t="inlineStr"/>
-      <c r="K104" s="5" t="inlineStr"/>
+        <v>57.6</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L104" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6952,80 +6930,88 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
+          <t>LONSDALE</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Lonsdale Power Station</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E105" s="5" t="inlineStr"/>
-      <c r="F105" s="5" t="inlineStr"/>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr"/>
-      <c r="I105" s="5" t="inlineStr"/>
-      <c r="J105" s="5" t="inlineStr"/>
-      <c r="K105" s="5" t="inlineStr"/>
-      <c r="L105" s="5" t="inlineStr"/>
-      <c r="M105" s="5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="M105" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="N105" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O105" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="O105" s="5" t="inlineStr"/>
       <c r="P105" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q105" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="Q105" s="5" t="inlineStr"/>
       <c r="R105" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S105" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="S105" s="5" t="inlineStr"/>
       <c r="T105" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U105" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V105" s="5" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="W105" s="6" t="n">
-        <v>-0.04</v>
-      </c>
+      <c r="V105" s="5" t="inlineStr"/>
+      <c r="W105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
+          <t>ADPMH1</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="5" t="inlineStr"/>
@@ -7033,7 +7019,9 @@
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr"/>
-      <c r="K106" s="5" t="inlineStr"/>
+      <c r="K106" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L106" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -7296,24 +7284,20 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>STANV1</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>Amcor Glass, Gawler Plant</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="3" t="inlineStr"/>
       <c r="E111" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0111</v>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
       <c r="G111" s="5" t="inlineStr"/>
@@ -7378,24 +7362,24 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>STANV1</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Tea Tree Gully Landfill Gas Power Station</t>
+          <t>Pt Stanvac Power Station</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
       <c r="G113" s="5" t="inlineStr"/>
@@ -7460,24 +7444,24 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>ANGASTON POWER STATION</t>
+          <t>Tea Tree Gully Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1.0061</v>
+        <v>1.0042</v>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
       <c r="G115" s="5" t="inlineStr"/>
@@ -7501,20 +7485,24 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Amcor Glass, Gawler Plant</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="3" t="inlineStr"/>
+          <t>ANGASTON POWER STATION</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="E116" s="5" t="n">
-        <v>1.0111</v>
+        <v>1.0061</v>
       </c>
       <c r="F116" s="5" t="inlineStr"/>
       <c r="G116" s="5" t="inlineStr"/>
@@ -7618,7 +7606,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>NPSNL2</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -7632,13 +7620,13 @@
         </is>
       </c>
       <c r="D119" s="4" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1.0482</v>
+        <v>0.9826</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>1.0791</v>
+        <v>1.0098</v>
       </c>
       <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="5" t="inlineStr"/>
@@ -7661,7 +7649,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -7675,13 +7663,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="G120" s="5" t="inlineStr"/>
       <c r="H120" s="5" t="inlineStr"/>
@@ -7704,7 +7692,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -7718,13 +7706,13 @@
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr"/>
@@ -7747,7 +7735,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL2</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -7761,13 +7749,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.9826</v>
+        <v>1.0482</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0791</v>
       </c>
       <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr"/>
@@ -7790,30 +7778,30 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>TERMSTOR</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
+          <t>Terminal Storage Mini Hydro Power Station</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D123" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>1.0051</v>
+        <v>1.0037</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.0047</v>
+        <v>1.0034</v>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr"/>
@@ -7880,30 +7868,30 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>TERMSTOR</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Terminal Storage Mini Hydro Power Station</t>
+          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0051</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>1.0034</v>
+        <v>1.0047</v>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr"/>
@@ -7925,7 +7913,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>TORRA2</t>
+          <t>TORRA4</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -7976,7 +7964,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>TORRA4</t>
+          <t>TORRA2</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -8180,33 +8168,41 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>TB2BG1</t>
+          <t>ADPBA1G</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D131" s="3" t="inlineStr"/>
+          <t>Adelaide Desalination Plant</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="E131" s="5" t="inlineStr"/>
       <c r="F131" s="5" t="inlineStr"/>
       <c r="G131" s="5" t="inlineStr"/>
       <c r="H131" s="5" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr"/>
-      <c r="J131" s="5" t="inlineStr"/>
-      <c r="K131" s="5" t="inlineStr"/>
+      <c r="J131" s="5" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L131" s="5" t="n">
-        <v>0.9966</v>
+        <v>1.0036</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0039</v>
       </c>
       <c r="N131" s="5" t="n">
-        <v>1.0102</v>
+        <v>1.0025</v>
       </c>
       <c r="O131" s="5" t="inlineStr"/>
       <c r="P131" s="5" t="inlineStr"/>
@@ -8221,12 +8217,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>DALNTH01</t>
+          <t>BOWWBA1G</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Dalrymple North BESS</t>
+          <t>Bolivar Waste Water Treatment Plant</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -8235,33 +8231,25 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="H132" s="5" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="I132" s="5" t="n">
-        <v>0.9045</v>
-      </c>
-      <c r="J132" s="5" t="n">
-        <v>0.9193</v>
-      </c>
+      <c r="G132" s="5" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr"/>
+      <c r="I132" s="5" t="inlineStr"/>
+      <c r="J132" s="5" t="inlineStr"/>
       <c r="K132" s="5" t="n">
-        <v>0.9212</v>
+        <v>1.0011</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>0.9432</v>
+        <v>1.0002</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.8954</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="N132" s="5" t="n">
-        <v>0.9092</v>
+        <v>1.0004</v>
       </c>
       <c r="O132" s="5" t="inlineStr"/>
       <c r="P132" s="5" t="inlineStr"/>
@@ -8276,12 +8264,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1G</t>
+          <t>CBWWBA1G</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Happy Valley WTP</t>
+          <t>Christies Beach WWTP</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -8290,7 +8278,7 @@
         </is>
       </c>
       <c r="D133" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="5" t="inlineStr"/>
@@ -8298,17 +8286,15 @@
       <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="inlineStr"/>
       <c r="J133" s="5" t="inlineStr"/>
-      <c r="K133" s="5" t="n">
-        <v>1.0052</v>
-      </c>
+      <c r="K133" s="5" t="inlineStr"/>
       <c r="L133" s="5" t="n">
-        <v>1.003</v>
+        <v>1.0036</v>
       </c>
       <c r="M133" s="5" t="n">
-        <v>1.0041</v>
+        <v>1.0039</v>
       </c>
       <c r="N133" s="5" t="n">
-        <v>1.0043</v>
+        <v>1.0025</v>
       </c>
       <c r="O133" s="5" t="inlineStr"/>
       <c r="P133" s="5" t="inlineStr"/>
@@ -8323,12 +8309,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>HPRG1</t>
+          <t>DALNTH01</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Power Reserve</t>
+          <t>Dalrymple North BESS</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -8337,33 +8323,33 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="5" t="inlineStr"/>
       <c r="G134" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.8848</v>
       </c>
       <c r="H134" s="5" t="n">
-        <v>0.9771</v>
+        <v>0.888</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>0.9851</v>
+        <v>0.9045</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>0.9838</v>
+        <v>0.9193</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>0.9772</v>
+        <v>0.9212</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9432</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.9653</v>
+        <v>0.8954</v>
       </c>
       <c r="N134" s="5" t="n">
-        <v>0.9657</v>
+        <v>0.9092</v>
       </c>
       <c r="O134" s="5" t="inlineStr"/>
       <c r="P134" s="5" t="inlineStr"/>
@@ -8378,12 +8364,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>LBBG1</t>
+          <t>HPRG1</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney BESS1</t>
+          <t>Hornsdale Power Reserve</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -8392,29 +8378,33 @@
         </is>
       </c>
       <c r="D135" s="4" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="E135" s="5" t="inlineStr"/>
       <c r="F135" s="5" t="inlineStr"/>
-      <c r="G135" s="5" t="inlineStr"/>
-      <c r="H135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>0.9771</v>
+      </c>
       <c r="I135" s="5" t="n">
-        <v>0.9922</v>
+        <v>0.9851</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>0.9741</v>
+        <v>0.9838</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>1.0022</v>
+        <v>0.9772</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0.9851</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="M135" s="5" t="n">
-        <v>0.979</v>
+        <v>0.9653</v>
       </c>
       <c r="N135" s="5" t="n">
-        <v>0.9841</v>
+        <v>0.9657</v>
       </c>
       <c r="O135" s="5" t="inlineStr"/>
       <c r="P135" s="5" t="inlineStr"/>
@@ -8429,12 +8419,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1G</t>
+          <t>HVWWBA1G</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Bolivar Waste Water Treatment Plant</t>
+          <t>Happy Valley WTP</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -8443,7 +8433,7 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="5" t="inlineStr"/>
@@ -8452,16 +8442,16 @@
       <c r="I136" s="5" t="inlineStr"/>
       <c r="J136" s="5" t="inlineStr"/>
       <c r="K136" s="5" t="n">
-        <v>1.0011</v>
+        <v>1.0052</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>1.0002</v>
+        <v>1.003</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.0041</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>1.0004</v>
+        <v>1.0043</v>
       </c>
       <c r="O136" s="5" t="inlineStr"/>
       <c r="P136" s="5" t="inlineStr"/>
@@ -8476,41 +8466,33 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1G</t>
+          <t>TB2BG1</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="n">
-        <v>7</v>
-      </c>
+          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D137" s="3" t="inlineStr"/>
       <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="5" t="inlineStr"/>
       <c r="G137" s="5" t="inlineStr"/>
       <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="inlineStr"/>
-      <c r="J137" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="K137" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="J137" s="5" t="inlineStr"/>
+      <c r="K137" s="5" t="inlineStr"/>
       <c r="L137" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9966</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>1.0039</v>
+        <v>1.0079</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0102</v>
       </c>
       <c r="O137" s="5" t="inlineStr"/>
       <c r="P137" s="5" t="inlineStr"/>
@@ -8525,12 +8507,12 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1G</t>
+          <t>LBBG1</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach WWTP</t>
+          <t>Lake Bonney BESS1</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -8539,23 +8521,29 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="5" t="inlineStr"/>
       <c r="G138" s="5" t="inlineStr"/>
       <c r="H138" s="5" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr"/>
-      <c r="J138" s="5" t="inlineStr"/>
-      <c r="K138" s="5" t="inlineStr"/>
+      <c r="I138" s="5" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>0.9741</v>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>1.0022</v>
+      </c>
       <c r="L138" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9851</v>
       </c>
       <c r="M138" s="5" t="n">
-        <v>1.0039</v>
+        <v>0.979</v>
       </c>
       <c r="N138" s="5" t="n">
-        <v>1.0025</v>
+        <v>0.9841</v>
       </c>
       <c r="O138" s="5" t="inlineStr"/>
       <c r="P138" s="5" t="inlineStr"/>
@@ -8932,7 +8920,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -9024,7 +9012,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -9116,12 +9104,14 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HDWF2</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr"/>
+          <t>HDWF1</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
       <c r="C12" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0.9799</v>
@@ -9160,15 +9150,11 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HDWF1</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0.9965000000000001</v>
-      </c>
+          <t>HDWF3</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -9206,11 +9192,13 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HDWF3</t>
+          <t>HDWF2</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="n">
+        <v>0.9918</v>
+      </c>
       <c r="D14" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -9376,7 +9364,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -9422,7 +9410,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -9692,7 +9680,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -9738,7 +9726,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -10082,7 +10070,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -10128,7 +10116,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -10566,7 +10554,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -10612,7 +10600,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -10810,7 +10798,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
@@ -10856,7 +10844,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -10902,7 +10890,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -10948,7 +10936,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
@@ -11040,7 +11028,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
+          <t>SMFBESS2</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr"/>
@@ -11070,7 +11058,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
+          <t>SMFBESS1</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr"/>
@@ -11130,7 +11118,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr"/>
@@ -11140,29 +11128,31 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="n">
-        <v>0.9966</v>
-      </c>
-      <c r="J62" s="5" t="n">
-        <v>1.0079</v>
-      </c>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="L62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="n">
+        <v>1.0102</v>
+      </c>
       <c r="M62" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="N62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="O62" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P62" s="5" t="inlineStr"/>
+      <c r="P62" s="5" t="n">
+        <v>0.9968</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr"/>
@@ -11172,26 +11162,24 @@
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="n">
+        <v>0.9966</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>1.0079</v>
+      </c>
       <c r="K63" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="L63" s="5" t="n">
-        <v>1.0102</v>
-      </c>
+      <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="N63" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+      <c r="N63" s="5" t="inlineStr"/>
       <c r="O63" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P63" s="5" t="n">
-        <v>0.9968</v>
-      </c>
+      <c r="P63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -11236,7 +11224,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT1</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -11282,7 +11270,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -11328,7 +11316,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT1</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -11752,34 +11740,42 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>BARKIPS1</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr"/>
-      <c r="C77" s="5" t="inlineStr"/>
-      <c r="D77" s="5" t="inlineStr"/>
-      <c r="E77" s="5" t="inlineStr"/>
+          <t>DG_SA1</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="F77" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="J77" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="L77" s="5" t="inlineStr"/>
       <c r="M77" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
       <c r="O77" s="5" t="n">
@@ -11790,42 +11786,34 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>TORNL1</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>BARKIPS1</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr"/>
+      <c r="C78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="J78" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="L78" s="5" t="inlineStr"/>
       <c r="M78" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
       <c r="O78" s="5" t="n">
@@ -11836,7 +11824,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
+          <t>TORNL1</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -11882,61 +11870,61 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr"/>
-      <c r="C80" s="5" t="inlineStr"/>
-      <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr"/>
-      <c r="J80" s="5" t="inlineStr"/>
+          <t>BOLIVAR1</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1.0012</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>1.0011</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
       <c r="K80" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="L80" s="5" t="n">
-        <v>1.0004</v>
-      </c>
+      <c r="L80" s="5" t="inlineStr"/>
       <c r="M80" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="N80" s="5" t="n">
-        <v>0.9999</v>
-      </c>
+      <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="P80" s="5" t="n">
-        <v>1.0002</v>
-      </c>
+      <c r="P80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>1.0012</v>
-      </c>
+          <t>BOWWPV1</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr"/>
+      <c r="C81" s="5" t="inlineStr"/>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -11996,7 +11984,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>BOWWPV1</t>
+          <t>BOWWBA1</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr"/>
@@ -12005,27 +11993,27 @@
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="5" t="inlineStr"/>
       <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="5" t="n">
-        <v>1.0011</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
+      <c r="H83" s="5" t="inlineStr"/>
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="5" t="inlineStr"/>
       <c r="K83" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="L83" s="5" t="inlineStr"/>
+      <c r="L83" s="5" t="n">
+        <v>1.0004</v>
+      </c>
       <c r="M83" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="N83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="n">
+        <v>0.9999</v>
+      </c>
       <c r="O83" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="P83" s="5" t="inlineStr"/>
+      <c r="P83" s="5" t="n">
+        <v>1.0002</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -12076,7 +12064,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>WINGF1_1</t>
+          <t>DRYCNL</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -12122,7 +12110,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>DRYCNL</t>
+          <t>WINGF1_1</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -12268,7 +12256,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1</t>
+          <t>HVWWPV1</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr"/>
@@ -12277,32 +12265,32 @@
       <c r="E90" s="5" t="inlineStr"/>
       <c r="F90" s="5" t="inlineStr"/>
       <c r="G90" s="5" t="inlineStr"/>
-      <c r="H90" s="5" t="inlineStr"/>
-      <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="n">
+        <v>1.0052</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>1.0041</v>
+      </c>
       <c r="K90" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="L90" s="5" t="n">
-        <v>1.0043</v>
-      </c>
+      <c r="L90" s="5" t="inlineStr"/>
       <c r="M90" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="N90" s="5" t="n">
-        <v>1.0024</v>
-      </c>
+      <c r="N90" s="5" t="inlineStr"/>
       <c r="O90" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P90" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="P90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>HVWWPV1</t>
+          <t>HVWWBA1</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr"/>
@@ -12311,27 +12299,27 @@
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="5" t="inlineStr"/>
       <c r="G91" s="5" t="inlineStr"/>
-      <c r="H91" s="5" t="n">
-        <v>1.0052</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>1.0041</v>
-      </c>
+      <c r="H91" s="5" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr"/>
+      <c r="J91" s="5" t="inlineStr"/>
       <c r="K91" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="L91" s="5" t="inlineStr"/>
+      <c r="L91" s="5" t="n">
+        <v>1.0043</v>
+      </c>
       <c r="M91" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="N91" s="5" t="inlineStr"/>
+      <c r="N91" s="5" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="O91" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P91" s="5" t="inlineStr"/>
+      <c r="P91" s="5" t="n">
+        <v>1.0022</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -12382,26 +12370,16 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C93" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>1.0053</v>
-      </c>
+          <t>ADPPV1</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr"/>
+      <c r="C93" s="5" t="inlineStr"/>
+      <c r="D93" s="5" t="inlineStr"/>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="5" t="inlineStr"/>
       <c r="G93" s="5" t="n">
-        <v>1.005</v>
+        <v>1.0038</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>1.0055</v>
@@ -12428,53 +12406,41 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C94" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>1.0039</v>
-      </c>
+          <t>ADPBA1</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr"/>
+      <c r="C94" s="5" t="inlineStr"/>
+      <c r="D94" s="5" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="5" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr"/>
+      <c r="J94" s="5" t="inlineStr"/>
       <c r="K94" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L94" s="5" t="inlineStr"/>
+      <c r="L94" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="M94" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N94" s="5" t="inlineStr"/>
+      <c r="N94" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="O94" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P94" s="5" t="inlineStr"/>
+      <c r="P94" s="5" t="n">
+        <v>1.0033</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
+          <t>ADPPV3</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr"/>
@@ -12508,27 +12474,15 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D96" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>1.005</v>
-      </c>
+          <t>ADPPV2</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr"/>
+      <c r="C96" s="5" t="inlineStr"/>
+      <c r="D96" s="5" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr"/>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
       <c r="H96" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -12554,15 +12508,27 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr"/>
-      <c r="C97" s="5" t="inlineStr"/>
-      <c r="D97" s="5" t="inlineStr"/>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
+          <t>STARHLWF</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>1.005</v>
+      </c>
       <c r="H97" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -12588,7 +12554,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
+          <t>CBWWPV1</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr"/>
@@ -12620,7 +12586,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
+          <t>CBWWDG2</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr"/>
@@ -12652,7 +12618,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>ADPPV1</t>
+          <t>CBWWDG1</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr"/>
@@ -12660,12 +12626,8 @@
       <c r="D100" s="5" t="inlineStr"/>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="5" t="inlineStr"/>
-      <c r="G100" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12688,7 +12650,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
+          <t>CBWWBG1</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr"/>
@@ -12698,31 +12660,29 @@
       <c r="F101" s="5" t="inlineStr"/>
       <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="5" t="inlineStr"/>
-      <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="5" t="inlineStr"/>
+      <c r="I101" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="K101" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L101" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N101" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="N101" s="5" t="inlineStr"/>
       <c r="O101" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P101" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="P101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>ADPMH1</t>
+          <t>CBWWBA1</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr"/>
@@ -12731,32 +12691,32 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="J102" s="5" t="n">
-        <v>1.0039</v>
-      </c>
+      <c r="H102" s="5" t="inlineStr"/>
+      <c r="I102" s="5" t="inlineStr"/>
+      <c r="J102" s="5" t="inlineStr"/>
       <c r="K102" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L102" s="5" t="inlineStr"/>
+      <c r="L102" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="M102" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N102" s="5" t="inlineStr"/>
+      <c r="N102" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="O102" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P102" s="5" t="inlineStr"/>
+      <c r="P102" s="5" t="n">
+        <v>1.0033</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG1</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr"/>
@@ -12788,16 +12748,30 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr"/>
-      <c r="C104" s="5" t="inlineStr"/>
-      <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr"/>
+          <t>PTSTAN1</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I104" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12820,41 +12794,53 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr"/>
-      <c r="C105" s="5" t="inlineStr"/>
-      <c r="D105" s="5" t="inlineStr"/>
-      <c r="E105" s="5" t="inlineStr"/>
-      <c r="F105" s="5" t="inlineStr"/>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr"/>
-      <c r="I105" s="5" t="inlineStr"/>
-      <c r="J105" s="5" t="inlineStr"/>
+          <t>LONSDALE</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="K105" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L105" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="L105" s="5" t="inlineStr"/>
       <c r="M105" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N105" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="N105" s="5" t="inlineStr"/>
       <c r="O105" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P105" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="P105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
+          <t>ADPMH1</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr"/>
@@ -12863,7 +12849,9 @@
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="5" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I106" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -13034,11 +13022,11 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>STANV1</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0111</v>
       </c>
       <c r="C111" s="5" t="inlineStr"/>
       <c r="D111" s="5" t="inlineStr"/>
@@ -13082,11 +13070,11 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>STANV1</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="C113" s="5" t="inlineStr"/>
       <c r="D113" s="5" t="inlineStr"/>
@@ -13130,11 +13118,11 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>1.0061</v>
+        <v>1.0042</v>
       </c>
       <c r="C115" s="5" t="inlineStr"/>
       <c r="D115" s="5" t="inlineStr"/>
@@ -13154,11 +13142,11 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>1.0111</v>
+        <v>1.0061</v>
       </c>
       <c r="C116" s="5" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr"/>
@@ -13228,14 +13216,14 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>NPSNL2</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>1.0482</v>
+        <v>0.9826</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1.0791</v>
+        <v>1.0098</v>
       </c>
       <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="5" t="inlineStr"/>
@@ -13254,14 +13242,14 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr"/>
@@ -13280,14 +13268,14 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="5" t="inlineStr"/>
@@ -13306,14 +13294,14 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL2</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
-        <v>0.9826</v>
+        <v>1.0482</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0791</v>
       </c>
       <c r="D122" s="5" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr"/>
@@ -13332,17 +13320,17 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>TERMSTOR</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1.0051</v>
+        <v>1.0037</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>1.0047</v>
+        <v>1.0034</v>
       </c>
       <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="5" t="inlineStr"/>
@@ -13388,17 +13376,17 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>TERMSTOR</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0051</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>1.0034</v>
+        <v>1.0047</v>
       </c>
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="5" t="inlineStr"/>
@@ -13416,7 +13404,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>TORRA2</t>
+          <t>TORRA4</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
@@ -13450,7 +13438,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>TORRA4</t>
+          <t>TORRA2</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
@@ -13586,7 +13574,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>TB2BG1</t>
+          <t>ADPBA1G</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr"/>
@@ -13594,16 +13582,20 @@
       <c r="D131" s="5" t="inlineStr"/>
       <c r="E131" s="5" t="inlineStr"/>
       <c r="F131" s="5" t="inlineStr"/>
-      <c r="G131" s="5" t="inlineStr"/>
-      <c r="H131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I131" s="5" t="n">
-        <v>0.9966</v>
+        <v>1.0036</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>1.0079</v>
+        <v>1.0039</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>1.0102</v>
+        <v>1.0025</v>
       </c>
       <c r="L131" s="5" t="inlineStr"/>
       <c r="M131" s="5" t="inlineStr"/>
@@ -13614,34 +13606,26 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>DALNTH01</t>
+          <t>BOWWBA1G</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr"/>
       <c r="C132" s="5" t="inlineStr"/>
-      <c r="D132" s="5" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="E132" s="5" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="F132" s="5" t="n">
-        <v>0.9045</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>0.9193</v>
-      </c>
+      <c r="D132" s="5" t="inlineStr"/>
+      <c r="E132" s="5" t="inlineStr"/>
+      <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr"/>
       <c r="H132" s="5" t="n">
-        <v>0.9212</v>
+        <v>1.0011</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>0.9432</v>
+        <v>1.0002</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>0.8954</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="K132" s="5" t="n">
-        <v>0.9092</v>
+        <v>1.0004</v>
       </c>
       <c r="L132" s="5" t="inlineStr"/>
       <c r="M132" s="5" t="inlineStr"/>
@@ -13652,7 +13636,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1G</t>
+          <t>CBWWBA1G</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr"/>
@@ -13661,17 +13645,15 @@
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="5" t="inlineStr"/>
       <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="n">
-        <v>1.0052</v>
-      </c>
+      <c r="H133" s="5" t="inlineStr"/>
       <c r="I133" s="5" t="n">
-        <v>1.003</v>
+        <v>1.0036</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>1.0041</v>
+        <v>1.0039</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>1.0043</v>
+        <v>1.0025</v>
       </c>
       <c r="L133" s="5" t="inlineStr"/>
       <c r="M133" s="5" t="inlineStr"/>
@@ -13682,34 +13664,34 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>HPRG1</t>
+          <t>DALNTH01</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr"/>
       <c r="C134" s="5" t="inlineStr"/>
       <c r="D134" s="5" t="n">
-        <v>0.9848</v>
+        <v>0.8848</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0.9771</v>
+        <v>0.888</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.9851</v>
+        <v>0.9045</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.9838</v>
+        <v>0.9193</v>
       </c>
       <c r="H134" s="5" t="n">
-        <v>0.9772</v>
+        <v>0.9212</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9432</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>0.9653</v>
+        <v>0.8954</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>0.9657</v>
+        <v>0.9092</v>
       </c>
       <c r="L134" s="5" t="inlineStr"/>
       <c r="M134" s="5" t="inlineStr"/>
@@ -13720,30 +13702,34 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>LBBG1</t>
+          <t>HPRG1</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr"/>
       <c r="C135" s="5" t="inlineStr"/>
-      <c r="D135" s="5" t="inlineStr"/>
-      <c r="E135" s="5" t="inlineStr"/>
+      <c r="D135" s="5" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0.9771</v>
+      </c>
       <c r="F135" s="5" t="n">
-        <v>0.9922</v>
+        <v>0.9851</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.9741</v>
+        <v>0.9838</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>1.0022</v>
+        <v>0.9772</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>0.9851</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>0.979</v>
+        <v>0.9653</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>0.9841</v>
+        <v>0.9657</v>
       </c>
       <c r="L135" s="5" t="inlineStr"/>
       <c r="M135" s="5" t="inlineStr"/>
@@ -13754,7 +13740,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1G</t>
+          <t>HVWWBA1G</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr"/>
@@ -13764,16 +13750,16 @@
       <c r="F136" s="5" t="inlineStr"/>
       <c r="G136" s="5" t="inlineStr"/>
       <c r="H136" s="5" t="n">
-        <v>1.0011</v>
+        <v>1.0052</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>1.0002</v>
+        <v>1.003</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.0041</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>1.0004</v>
+        <v>1.0043</v>
       </c>
       <c r="L136" s="5" t="inlineStr"/>
       <c r="M136" s="5" t="inlineStr"/>
@@ -13784,7 +13770,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1G</t>
+          <t>TB2BG1</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr"/>
@@ -13792,20 +13778,16 @@
       <c r="D137" s="5" t="inlineStr"/>
       <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="5" t="inlineStr"/>
-      <c r="G137" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="H137" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="G137" s="5" t="inlineStr"/>
+      <c r="H137" s="5" t="inlineStr"/>
       <c r="I137" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9966</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>1.0039</v>
+        <v>1.0079</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>1.0025</v>
+        <v>1.0102</v>
       </c>
       <c r="L137" s="5" t="inlineStr"/>
       <c r="M137" s="5" t="inlineStr"/>
@@ -13816,24 +13798,30 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1G</t>
+          <t>LBBG1</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr"/>
       <c r="C138" s="5" t="inlineStr"/>
       <c r="D138" s="5" t="inlineStr"/>
       <c r="E138" s="5" t="inlineStr"/>
-      <c r="F138" s="5" t="inlineStr"/>
-      <c r="G138" s="5" t="inlineStr"/>
-      <c r="H138" s="5" t="inlineStr"/>
+      <c r="F138" s="5" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.9741</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>1.0022</v>
+      </c>
       <c r="I138" s="5" t="n">
-        <v>1.0036</v>
+        <v>0.9851</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>1.0039</v>
+        <v>0.979</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>1.0025</v>
+        <v>0.9841</v>
       </c>
       <c r="L138" s="5" t="inlineStr"/>
       <c r="M138" s="5" t="inlineStr"/>
@@ -14468,18 +14456,16 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
+          <t>SMFBESS2</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 1</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
+          <t>SMFBESS2</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v/>
       </c>
       <c r="D16" s="5" t="n">
         <v>0.9953</v>
@@ -14497,18 +14483,16 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
+          <t>SMFBESS1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 2</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
+          <t>SMFBESS1</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v/>
       </c>
       <c r="D17" s="5" t="n">
         <v>0.9953</v>
@@ -14715,7 +14699,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -14744,7 +14728,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -14889,12 +14873,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -14947,12 +14931,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -15092,7 +15076,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -15102,7 +15086,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -15121,7 +15105,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -15131,7 +15115,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">

--- a/outputs/SA_mlf.xlsx
+++ b/outputs/SA_mlf.xlsx
@@ -3750,13 +3750,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>TB3BESS</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D52" s="3" t="inlineStr"/>
+          <t>Tailem Bend 3 BESS</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>263</v>
+      </c>
       <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr"/>
@@ -4191,13 +4195,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D59" s="3" t="inlineStr"/>
+          <t>Summerfield BESS 2</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>153.65</v>
+      </c>
       <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr"/>
@@ -4242,13 +4250,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D60" s="3" t="inlineStr"/>
+          <t>Summerfield BESS 1</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>153.65</v>
+      </c>
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="5" t="inlineStr"/>
       <c r="G60" s="5" t="inlineStr"/>
@@ -5037,7 +5049,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Torrens Island Power Station</t>
+          <t>TORRENS ISLAND POWER STATION</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -14461,11 +14473,13 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v/>
+          <t>Summerfield BESS 2</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
       </c>
       <c r="D16" s="5" t="n">
         <v>0.9953</v>
@@ -14488,11 +14502,13 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v/>
+          <t>Summerfield BESS 1</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>0.9953</v>

--- a/outputs/SA_mlf.xlsx
+++ b/outputs/SA_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W138"/>
+  <dimension ref="A1:W129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -761,13 +761,27 @@
       </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="n">
+        <v>0.8848</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.9045</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.9212</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0.9432</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0.8954</v>
+      </c>
       <c r="N4" s="5" t="n">
         <v>0.9092</v>
       </c>
@@ -991,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1005,7 +1019,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>39</v>
+        <v>80.5</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>0.9352</v>
@@ -1125,12 +1139,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1139,7 +1153,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>80.5</v>
+        <v>39</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>0.9352</v>
@@ -1259,12 +1273,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HDWF1</t>
+          <t>HDWF2</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm</t>
+          <t>Hornsdale Wind Farm 2</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1275,11 +1289,9 @@
       <c r="D12" s="4" t="n">
         <v>102.4</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
+      <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9918</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0.9799</v>
@@ -1326,12 +1338,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HDWF3</t>
+          <t>HDWF1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 3</t>
+          <t>Hornsdale Wind Farm</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1340,10 +1352,14 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
+        <v>102.4</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.9965000000000001</v>
+      </c>
       <c r="G13" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -1389,12 +1405,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HDWF2</t>
+          <t>HDWF3</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 2</t>
+          <t>Hornsdale Wind Farm 3</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1403,12 +1419,10 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>102.4</v>
+        <v>112</v>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="n">
-        <v>0.9918</v>
-      </c>
+      <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -1645,7 +1659,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1712,7 +1726,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2108,21 +2122,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Hallett Power Station</t>
+          <t>Hallett 1 Wind Farm</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>217</v>
+        <v>94.5</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0.9835</v>
@@ -2175,21 +2189,21 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Hallett 1 Wind Farm</t>
+          <t>Hallett Power Station</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>94.5</v>
+        <v>217</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9835</v>
@@ -2704,13 +2718,27 @@
       </c>
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0.9772</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0.9651999999999999</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0.9653</v>
+      </c>
       <c r="N35" s="5" t="n">
         <v>0.9657</v>
       </c>
@@ -2745,12 +2773,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Snowtown South Wind Farm</t>
+          <t>Snowtown Wind Farm Stage 2 North</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2759,7 +2787,7 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>0.9782</v>
@@ -2812,12 +2840,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Stage 2 North</t>
+          <t>Snowtown South Wind Farm</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2826,7 +2854,7 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>0.9782</v>
@@ -3312,11 +3340,21 @@
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0.9741</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0.979</v>
+      </c>
       <c r="N45" s="5" t="n">
         <v>0.9841</v>
       </c>
@@ -3485,7 +3523,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3552,7 +3590,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3855,7 +3893,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3922,7 +3960,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3936,7 +3974,7 @@
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0.9932</v>
@@ -3989,7 +4027,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4003,7 +4041,7 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>0.9932</v>
@@ -4056,7 +4094,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4070,7 +4108,7 @@
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0.9932</v>
@@ -4190,12 +4228,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
+          <t>SMFBESS1</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 2</t>
+          <t>Summerfield BESS 1</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4245,12 +4283,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
+          <t>SMFBESS2</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 1</t>
+          <t>Summerfield BESS 2</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4351,7 +4389,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4361,11 +4399,11 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="5" t="inlineStr"/>
@@ -4374,43 +4412,37 @@
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr"/>
-      <c r="L62" s="5" t="inlineStr"/>
-      <c r="M62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="n">
+        <v>0.9966</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>1.0079</v>
+      </c>
       <c r="N62" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="O62" s="5" t="n">
-        <v>1.0102</v>
-      </c>
+      <c r="O62" s="5" t="inlineStr"/>
       <c r="P62" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="Q62" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+      <c r="Q62" s="5" t="inlineStr"/>
       <c r="R62" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="S62" s="5" t="n">
-        <v>0.9968</v>
-      </c>
+      <c r="S62" s="5" t="inlineStr"/>
       <c r="T62" s="5" t="n">
         <v>0.0023</v>
       </c>
       <c r="U62" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="V62" s="5" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="W62" s="6" t="n">
-        <v>0.23</v>
-      </c>
+      <c r="V62" s="5" t="inlineStr"/>
+      <c r="W62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4420,11 +4452,11 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="5" t="inlineStr"/>
@@ -4442,23 +4474,33 @@
       <c r="N63" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="O63" s="5" t="inlineStr"/>
+      <c r="O63" s="5" t="n">
+        <v>1.0102</v>
+      </c>
       <c r="P63" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="Q63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="R63" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="S63" s="5" t="inlineStr"/>
+      <c r="S63" s="5" t="n">
+        <v>0.9968</v>
+      </c>
       <c r="T63" s="5" t="n">
         <v>0.0023</v>
       </c>
       <c r="U63" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="V63" s="5" t="inlineStr"/>
-      <c r="W63" s="6" t="inlineStr"/>
+      <c r="V63" s="5" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="W63" s="6" t="n">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -4524,7 +4566,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT1</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4591,7 +4633,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4658,7 +4700,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT1</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5201,8 +5243,12 @@
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="5" t="inlineStr"/>
       <c r="K75" s="5" t="inlineStr"/>
-      <c r="L75" s="5" t="inlineStr"/>
-      <c r="M75" s="5" t="inlineStr"/>
+      <c r="L75" s="5" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>0.9996</v>
+      </c>
       <c r="N75" s="5" t="n">
         <v>0.9998</v>
       </c>
@@ -5292,51 +5338,47 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
+          <t>BARKIPS1</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>SA1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr"/>
+          <t>Barker Inlet Power Station</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D77" s="4" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
       <c r="I77" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="O77" s="5" t="inlineStr"/>
       <c r="P77" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="Q77" s="5" t="inlineStr"/>
       <c r="R77" s="5" t="n">
@@ -5344,10 +5386,10 @@
       </c>
       <c r="S77" s="5" t="inlineStr"/>
       <c r="T77" s="5" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="U77" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="V77" s="5" t="inlineStr"/>
       <c r="W77" s="6" t="inlineStr"/>
@@ -5355,12 +5397,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>BARKIPS1</t>
+          <t>TORNL1</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Barker Inlet Power Station</t>
+          <t>TORRENS ISLAND POWER STATION</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5369,33 +5411,41 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>211</v>
-      </c>
-      <c r="E78" s="5" t="inlineStr"/>
-      <c r="F78" s="5" t="inlineStr"/>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I78" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="M78" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="O78" s="5" t="inlineStr"/>
       <c r="P78" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="Q78" s="5" t="inlineStr"/>
       <c r="R78" s="5" t="n">
@@ -5403,10 +5453,10 @@
       </c>
       <c r="S78" s="5" t="inlineStr"/>
       <c r="T78" s="5" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="U78" s="6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="V78" s="5" t="inlineStr"/>
       <c r="W78" s="6" t="inlineStr"/>
@@ -5414,21 +5464,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>TORNL1</t>
+          <t>DG_SA1</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>TORRENS ISLAND POWER STATION</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
+          <t>SA1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n"/>
       <c r="D79" s="4" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="E79" s="5" t="n">
         <v>1</v>
@@ -5481,7 +5527,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
+          <t>BOWWBA1</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -5491,30 +5537,18 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="J80" s="5" t="n">
-        <v>1.0012</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
       <c r="K80" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -5527,28 +5561,38 @@
       <c r="N80" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="O80" s="5" t="inlineStr"/>
+      <c r="O80" s="5" t="n">
+        <v>1.0004</v>
+      </c>
       <c r="P80" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="Q80" s="5" t="inlineStr"/>
+      <c r="Q80" s="5" t="n">
+        <v>0.9999</v>
+      </c>
       <c r="R80" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="S80" s="5" t="inlineStr"/>
+      <c r="S80" s="5" t="n">
+        <v>1.0002</v>
+      </c>
       <c r="T80" s="5" t="n">
         <v>0.0003</v>
       </c>
       <c r="U80" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V80" s="5" t="inlineStr"/>
-      <c r="W80" s="6" t="inlineStr"/>
+      <c r="V80" s="5" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="W80" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>BOWWPV1</t>
+          <t>BOLIVAR1</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5558,18 +5602,30 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="E81" s="5" t="inlineStr"/>
-      <c r="F81" s="5" t="inlineStr"/>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="5" t="inlineStr"/>
+        <v>9.9</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>1.0012</v>
+      </c>
       <c r="K81" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -5658,7 +5714,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1</t>
+          <t>BOWWPV1</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5668,11 +5724,11 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>3</v>
+        <v>8.25</v>
       </c>
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="5" t="inlineStr"/>
@@ -5680,39 +5736,35 @@
       <c r="H83" s="5" t="inlineStr"/>
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr"/>
-      <c r="K83" s="5" t="inlineStr"/>
-      <c r="L83" s="5" t="inlineStr"/>
-      <c r="M83" s="5" t="inlineStr"/>
+      <c r="K83" s="5" t="n">
+        <v>1.0011</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
       <c r="N83" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="O83" s="5" t="n">
-        <v>1.0004</v>
-      </c>
+      <c r="O83" s="5" t="inlineStr"/>
       <c r="P83" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="Q83" s="5" t="n">
-        <v>0.9999</v>
-      </c>
+      <c r="Q83" s="5" t="inlineStr"/>
       <c r="R83" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="S83" s="5" t="n">
-        <v>1.0002</v>
-      </c>
+      <c r="S83" s="5" t="inlineStr"/>
       <c r="T83" s="5" t="n">
         <v>0.0003</v>
       </c>
       <c r="U83" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V83" s="5" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="W83" s="6" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="V83" s="5" t="inlineStr"/>
+      <c r="W83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -5784,18 +5836,22 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>DRYCNL</t>
+          <t>WINGF1_1</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Dry Creek Gas Turbine Station</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D85" s="3" t="inlineStr"/>
+          <t>Wingfield 1 Landfill Gas Power Station</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Other Renewable</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>4.12</v>
+      </c>
       <c r="E85" s="5" t="n">
         <v>1.0029</v>
       </c>
@@ -5847,21 +5903,21 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>WINGF1_1</t>
+          <t>DRYCNL</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Wingfield 1 Landfill Gas Power Station</t>
+          <t>Dry Creek Gas Turbine Station</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>4.12</v>
+        <v>50</v>
       </c>
       <c r="E86" s="5" t="n">
         <v>1.0029</v>
@@ -6077,7 +6133,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>HVWWPV1</t>
+          <t>HVWWBA1</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -6087,11 +6143,11 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E90" s="5" t="inlineStr"/>
       <c r="F90" s="5" t="inlineStr"/>
@@ -6111,28 +6167,38 @@
       <c r="N90" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="O90" s="5" t="inlineStr"/>
+      <c r="O90" s="5" t="n">
+        <v>1.0043</v>
+      </c>
       <c r="P90" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="Q90" s="5" t="inlineStr"/>
+      <c r="Q90" s="5" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="R90" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="S90" s="5" t="inlineStr"/>
+      <c r="S90" s="5" t="n">
+        <v>1.0022</v>
+      </c>
       <c r="T90" s="5" t="n">
         <v>-0.0002</v>
       </c>
       <c r="U90" s="6" t="n">
         <v>-0.02</v>
       </c>
-      <c r="V90" s="5" t="inlineStr"/>
-      <c r="W90" s="6" t="inlineStr"/>
+      <c r="V90" s="5" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="W90" s="6" t="n">
+        <v>-0.02</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1</t>
+          <t>HVWWPV1</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -6142,11 +6208,11 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="5" t="inlineStr"/>
@@ -6154,39 +6220,35 @@
       <c r="H91" s="5" t="inlineStr"/>
       <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="5" t="inlineStr"/>
-      <c r="K91" s="5" t="inlineStr"/>
-      <c r="L91" s="5" t="inlineStr"/>
-      <c r="M91" s="5" t="inlineStr"/>
+      <c r="K91" s="5" t="n">
+        <v>1.0052</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>1.0041</v>
+      </c>
       <c r="N91" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="O91" s="5" t="n">
-        <v>1.0043</v>
-      </c>
+      <c r="O91" s="5" t="inlineStr"/>
       <c r="P91" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="Q91" s="5" t="n">
-        <v>1.0024</v>
-      </c>
+      <c r="Q91" s="5" t="inlineStr"/>
       <c r="R91" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="S91" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="S91" s="5" t="inlineStr"/>
       <c r="T91" s="5" t="n">
         <v>-0.0002</v>
       </c>
       <c r="U91" s="6" t="n">
         <v>-0.02</v>
       </c>
-      <c r="V91" s="5" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="W91" s="6" t="n">
-        <v>-0.02</v>
-      </c>
+      <c r="V91" s="5" t="inlineStr"/>
+      <c r="W91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -6258,29 +6320,39 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>ADPPV1</t>
+          <t>PTSTAN1</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Pt Stanvac Power Station</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="E93" s="5" t="inlineStr"/>
-      <c r="F93" s="5" t="inlineStr"/>
-      <c r="G93" s="5" t="inlineStr"/>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
+        <v>57.6</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>1.0053</v>
+      </c>
       <c r="J93" s="5" t="n">
-        <v>1.0038</v>
+        <v>1.005</v>
       </c>
       <c r="K93" s="5" t="n">
         <v>1.0055</v>
@@ -6315,66 +6387,74 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
+          <t>STARHLWF</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Starfish Hill Wind Farm</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="5" t="inlineStr"/>
-      <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr"/>
-      <c r="J94" s="5" t="inlineStr"/>
-      <c r="K94" s="5" t="inlineStr"/>
-      <c r="L94" s="5" t="inlineStr"/>
-      <c r="M94" s="5" t="inlineStr"/>
+        <v>34.5</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="N94" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O94" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="O94" s="5" t="inlineStr"/>
       <c r="P94" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q94" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="Q94" s="5" t="inlineStr"/>
       <c r="R94" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S94" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="S94" s="5" t="inlineStr"/>
       <c r="T94" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U94" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V94" s="5" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="W94" s="6" t="n">
-        <v>-0.04</v>
-      </c>
+      <c r="V94" s="5" t="inlineStr"/>
+      <c r="W94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
+          <t>ADPPV2</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -6388,7 +6468,7 @@
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="5" t="inlineStr"/>
@@ -6429,28 +6509,40 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
+          <t>LONSDALE</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Lonsdale Power Station</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="5" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>1.005</v>
+      </c>
       <c r="K96" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -6484,40 +6576,28 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
+          <t>ADPPV3</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Starfish Hill Wind Farm</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I97" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J97" s="5" t="n">
-        <v>1.005</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="E97" s="5" t="inlineStr"/>
+      <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr"/>
+      <c r="H97" s="5" t="inlineStr"/>
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="5" t="inlineStr"/>
       <c r="K97" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -6551,7 +6631,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -6565,7 +6645,7 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>2.75</v>
+        <v>1.08</v>
       </c>
       <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="5" t="inlineStr"/>
@@ -6604,7 +6684,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
+          <t>CBWWPV1</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -6614,11 +6694,11 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>0.72</v>
+        <v>2.75</v>
       </c>
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="5" t="inlineStr"/>
@@ -6657,29 +6737,33 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG1</t>
+          <t>ADPPV1</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>2</v>
+        <v>24.75</v>
       </c>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr"/>
-      <c r="J100" s="5" t="inlineStr"/>
-      <c r="K100" s="5" t="inlineStr"/>
+      <c r="J100" s="5" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L100" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6710,29 +6794,33 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
+          <t>ADPBA1</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>0.664</v>
+        <v>7.76</v>
       </c>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr"/>
       <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="5" t="inlineStr"/>
-      <c r="K101" s="5" t="inlineStr"/>
+      <c r="J101" s="5" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L101" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6742,42 +6830,52 @@
       <c r="N101" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O101" s="5" t="inlineStr"/>
+      <c r="O101" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="P101" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q101" s="5" t="inlineStr"/>
+      <c r="Q101" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="R101" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S101" s="5" t="inlineStr"/>
+      <c r="S101" s="5" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="T101" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U101" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V101" s="5" t="inlineStr"/>
-      <c r="W101" s="6" t="inlineStr"/>
+      <c r="V101" s="5" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="W101" s="6" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
+          <t>ADPMH1</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="5" t="inlineStr"/>
@@ -6785,44 +6883,40 @@
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr"/>
-      <c r="K102" s="5" t="inlineStr"/>
-      <c r="L102" s="5" t="inlineStr"/>
-      <c r="M102" s="5" t="inlineStr"/>
+      <c r="K102" s="5" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="M102" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="N102" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O102" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="O102" s="5" t="inlineStr"/>
       <c r="P102" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q102" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="Q102" s="5" t="inlineStr"/>
       <c r="R102" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S102" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="S102" s="5" t="inlineStr"/>
       <c r="T102" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U102" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V102" s="5" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="W102" s="6" t="n">
-        <v>-0.04</v>
-      </c>
+      <c r="V102" s="5" t="inlineStr"/>
+      <c r="W102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
+          <t>CBWWDG1</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -6832,11 +6926,11 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>1.08</v>
+        <v>2</v>
       </c>
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="5" t="inlineStr"/>
@@ -6875,43 +6969,29 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
+          <t>CBWWBG1</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I104" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J104" s="5" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="K104" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+        <v>0.664</v>
+      </c>
+      <c r="E104" s="5" t="inlineStr"/>
+      <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="5" t="inlineStr"/>
+      <c r="I104" s="5" t="inlineStr"/>
+      <c r="J104" s="5" t="inlineStr"/>
+      <c r="K104" s="5" t="inlineStr"/>
       <c r="L104" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6942,43 +7022,29 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
+          <t>CBWWBA1</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Lonsdale Power Station</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E105" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J105" s="5" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="K105" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+        <v>2.16</v>
+      </c>
+      <c r="E105" s="5" t="inlineStr"/>
+      <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr"/>
+      <c r="I105" s="5" t="inlineStr"/>
+      <c r="J105" s="5" t="inlineStr"/>
+      <c r="K105" s="5" t="inlineStr"/>
       <c r="L105" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6988,42 +7054,52 @@
       <c r="N105" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O105" s="5" t="inlineStr"/>
+      <c r="O105" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="P105" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q105" s="5" t="inlineStr"/>
+      <c r="Q105" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="R105" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S105" s="5" t="inlineStr"/>
+      <c r="S105" s="5" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="T105" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U105" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V105" s="5" t="inlineStr"/>
-      <c r="W105" s="6" t="inlineStr"/>
+      <c r="V105" s="5" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="W105" s="6" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>ADPMH1</t>
+          <t>CBWWDG2</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>1.44</v>
+        <v>0.72</v>
       </c>
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="5" t="inlineStr"/>
@@ -7031,9 +7107,7 @@
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr"/>
-      <c r="K106" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="K106" s="5" t="inlineStr"/>
       <c r="L106" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -7296,20 +7370,24 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>STANV1</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Amcor Glass, Gawler Plant</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D111" s="3" t="inlineStr"/>
+          <t>Pt Stanvac Power Station</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>58</v>
+      </c>
       <c r="E111" s="5" t="n">
-        <v>1.0111</v>
+        <v>1.0075</v>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
       <c r="G111" s="5" t="inlineStr"/>
@@ -7374,24 +7452,24 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>STANV1</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
+          <t>Tea Tree Gully Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
       <c r="G113" s="5" t="inlineStr"/>
@@ -7456,24 +7534,24 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Tea Tree Gully Landfill Gas Power Station</t>
+          <t>ANGASTON POWER STATION</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0061</v>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
       <c r="G115" s="5" t="inlineStr"/>
@@ -7497,12 +7575,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ANGASTON POWER STATION</t>
+          <t>Amcor Glass, Gawler Plant</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -7511,10 +7589,10 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1.0061</v>
+        <v>1.0111</v>
       </c>
       <c r="F116" s="5" t="inlineStr"/>
       <c r="G116" s="5" t="inlineStr"/>
@@ -7587,10 +7665,14 @@
           <t>Playford B Power Station</t>
         </is>
       </c>
-      <c r="C118" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D118" s="3" t="inlineStr"/>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>240</v>
+      </c>
       <c r="E118" s="5" t="n">
         <v>0.9881</v>
       </c>
@@ -7618,7 +7700,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>NPSNL2</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -7632,13 +7714,13 @@
         </is>
       </c>
       <c r="D119" s="4" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0.9826</v>
+        <v>1.0482</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0791</v>
       </c>
       <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="5" t="inlineStr"/>
@@ -7661,7 +7743,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -7675,13 +7757,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="G120" s="5" t="inlineStr"/>
       <c r="H120" s="5" t="inlineStr"/>
@@ -7704,7 +7786,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -7718,13 +7800,13 @@
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr"/>
@@ -7747,7 +7829,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>NPSNL2</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -7761,13 +7843,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1.0482</v>
+        <v>0.9826</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>1.0791</v>
+        <v>1.0098</v>
       </c>
       <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr"/>
@@ -7790,30 +7872,30 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>TERMSTOR</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Terminal Storage Mini Hydro Power Station</t>
+          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D123" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0051</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.0034</v>
+        <v>1.0047</v>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr"/>
@@ -7880,30 +7962,30 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>TERMSTOR</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
+          <t>Terminal Storage Mini Hydro Power Station</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>1.0051</v>
+        <v>1.0037</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>1.0047</v>
+        <v>1.0034</v>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr"/>
@@ -7925,7 +8007,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>TORRA4</t>
+          <t>TORRA2</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -7976,7 +8058,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>TORRA2</t>
+          <t>TORRA4</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -8132,441 +8214,6 @@
       <c r="V129" s="5" t="inlineStr"/>
       <c r="W129" s="6" t="inlineStr"/>
     </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>TIBG1</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>Torrens Island BESS</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="5" t="inlineStr"/>
-      <c r="G130" s="5" t="inlineStr"/>
-      <c r="H130" s="5" t="inlineStr"/>
-      <c r="I130" s="5" t="inlineStr"/>
-      <c r="J130" s="5" t="inlineStr"/>
-      <c r="K130" s="5" t="inlineStr"/>
-      <c r="L130" s="5" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="M130" s="5" t="n">
-        <v>0.9996</v>
-      </c>
-      <c r="N130" s="5" t="n">
-        <v>0.9998</v>
-      </c>
-      <c r="O130" s="5" t="inlineStr"/>
-      <c r="P130" s="5" t="inlineStr"/>
-      <c r="Q130" s="5" t="inlineStr"/>
-      <c r="R130" s="5" t="inlineStr"/>
-      <c r="S130" s="5" t="inlineStr"/>
-      <c r="T130" s="5" t="inlineStr"/>
-      <c r="U130" s="6" t="inlineStr"/>
-      <c r="V130" s="5" t="inlineStr"/>
-      <c r="W130" s="6" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>ADPBA1G</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>Adelaide Desalination Plant</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E131" s="5" t="inlineStr"/>
-      <c r="F131" s="5" t="inlineStr"/>
-      <c r="G131" s="5" t="inlineStr"/>
-      <c r="H131" s="5" t="inlineStr"/>
-      <c r="I131" s="5" t="inlineStr"/>
-      <c r="J131" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="M131" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v>1.0025</v>
-      </c>
-      <c r="O131" s="5" t="inlineStr"/>
-      <c r="P131" s="5" t="inlineStr"/>
-      <c r="Q131" s="5" t="inlineStr"/>
-      <c r="R131" s="5" t="inlineStr"/>
-      <c r="S131" s="5" t="inlineStr"/>
-      <c r="T131" s="5" t="inlineStr"/>
-      <c r="U131" s="6" t="inlineStr"/>
-      <c r="V131" s="5" t="inlineStr"/>
-      <c r="W131" s="6" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>BOWWBA1G</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>Bolivar Waste Water Treatment Plant</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E132" s="5" t="inlineStr"/>
-      <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="inlineStr"/>
-      <c r="I132" s="5" t="inlineStr"/>
-      <c r="J132" s="5" t="inlineStr"/>
-      <c r="K132" s="5" t="n">
-        <v>1.0011</v>
-      </c>
-      <c r="L132" s="5" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="M132" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="N132" s="5" t="n">
-        <v>1.0004</v>
-      </c>
-      <c r="O132" s="5" t="inlineStr"/>
-      <c r="P132" s="5" t="inlineStr"/>
-      <c r="Q132" s="5" t="inlineStr"/>
-      <c r="R132" s="5" t="inlineStr"/>
-      <c r="S132" s="5" t="inlineStr"/>
-      <c r="T132" s="5" t="inlineStr"/>
-      <c r="U132" s="6" t="inlineStr"/>
-      <c r="V132" s="5" t="inlineStr"/>
-      <c r="W132" s="6" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>CBWWBA1G</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>Christies Beach WWTP</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E133" s="5" t="inlineStr"/>
-      <c r="F133" s="5" t="inlineStr"/>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr"/>
-      <c r="I133" s="5" t="inlineStr"/>
-      <c r="J133" s="5" t="inlineStr"/>
-      <c r="K133" s="5" t="inlineStr"/>
-      <c r="L133" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="M133" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="N133" s="5" t="n">
-        <v>1.0025</v>
-      </c>
-      <c r="O133" s="5" t="inlineStr"/>
-      <c r="P133" s="5" t="inlineStr"/>
-      <c r="Q133" s="5" t="inlineStr"/>
-      <c r="R133" s="5" t="inlineStr"/>
-      <c r="S133" s="5" t="inlineStr"/>
-      <c r="T133" s="5" t="inlineStr"/>
-      <c r="U133" s="6" t="inlineStr"/>
-      <c r="V133" s="5" t="inlineStr"/>
-      <c r="W133" s="6" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>DALNTH01</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>Dalrymple North BESS</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E134" s="5" t="inlineStr"/>
-      <c r="F134" s="5" t="inlineStr"/>
-      <c r="G134" s="5" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="I134" s="5" t="n">
-        <v>0.9045</v>
-      </c>
-      <c r="J134" s="5" t="n">
-        <v>0.9193</v>
-      </c>
-      <c r="K134" s="5" t="n">
-        <v>0.9212</v>
-      </c>
-      <c r="L134" s="5" t="n">
-        <v>0.9432</v>
-      </c>
-      <c r="M134" s="5" t="n">
-        <v>0.8954</v>
-      </c>
-      <c r="N134" s="5" t="n">
-        <v>0.9092</v>
-      </c>
-      <c r="O134" s="5" t="inlineStr"/>
-      <c r="P134" s="5" t="inlineStr"/>
-      <c r="Q134" s="5" t="inlineStr"/>
-      <c r="R134" s="5" t="inlineStr"/>
-      <c r="S134" s="5" t="inlineStr"/>
-      <c r="T134" s="5" t="inlineStr"/>
-      <c r="U134" s="6" t="inlineStr"/>
-      <c r="V134" s="5" t="inlineStr"/>
-      <c r="W134" s="6" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>HPRG1</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>Hornsdale Power Reserve</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="E135" s="5" t="inlineStr"/>
-      <c r="F135" s="5" t="inlineStr"/>
-      <c r="G135" s="5" t="n">
-        <v>0.9848</v>
-      </c>
-      <c r="H135" s="5" t="n">
-        <v>0.9771</v>
-      </c>
-      <c r="I135" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="J135" s="5" t="n">
-        <v>0.9838</v>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>0.9772</v>
-      </c>
-      <c r="L135" s="5" t="n">
-        <v>0.9651999999999999</v>
-      </c>
-      <c r="M135" s="5" t="n">
-        <v>0.9653</v>
-      </c>
-      <c r="N135" s="5" t="n">
-        <v>0.9657</v>
-      </c>
-      <c r="O135" s="5" t="inlineStr"/>
-      <c r="P135" s="5" t="inlineStr"/>
-      <c r="Q135" s="5" t="inlineStr"/>
-      <c r="R135" s="5" t="inlineStr"/>
-      <c r="S135" s="5" t="inlineStr"/>
-      <c r="T135" s="5" t="inlineStr"/>
-      <c r="U135" s="6" t="inlineStr"/>
-      <c r="V135" s="5" t="inlineStr"/>
-      <c r="W135" s="6" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>HVWWBA1G</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>Happy Valley WTP</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E136" s="5" t="inlineStr"/>
-      <c r="F136" s="5" t="inlineStr"/>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="inlineStr"/>
-      <c r="I136" s="5" t="inlineStr"/>
-      <c r="J136" s="5" t="inlineStr"/>
-      <c r="K136" s="5" t="n">
-        <v>1.0052</v>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="M136" s="5" t="n">
-        <v>1.0041</v>
-      </c>
-      <c r="N136" s="5" t="n">
-        <v>1.0043</v>
-      </c>
-      <c r="O136" s="5" t="inlineStr"/>
-      <c r="P136" s="5" t="inlineStr"/>
-      <c r="Q136" s="5" t="inlineStr"/>
-      <c r="R136" s="5" t="inlineStr"/>
-      <c r="S136" s="5" t="inlineStr"/>
-      <c r="T136" s="5" t="inlineStr"/>
-      <c r="U136" s="6" t="inlineStr"/>
-      <c r="V136" s="5" t="inlineStr"/>
-      <c r="W136" s="6" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>TB2BG1</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>Tailem Bend 2 Hybrid Renewable Power Station</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D137" s="3" t="inlineStr"/>
-      <c r="E137" s="5" t="inlineStr"/>
-      <c r="F137" s="5" t="inlineStr"/>
-      <c r="G137" s="5" t="inlineStr"/>
-      <c r="H137" s="5" t="inlineStr"/>
-      <c r="I137" s="5" t="inlineStr"/>
-      <c r="J137" s="5" t="inlineStr"/>
-      <c r="K137" s="5" t="inlineStr"/>
-      <c r="L137" s="5" t="n">
-        <v>0.9966</v>
-      </c>
-      <c r="M137" s="5" t="n">
-        <v>1.0079</v>
-      </c>
-      <c r="N137" s="5" t="n">
-        <v>1.0102</v>
-      </c>
-      <c r="O137" s="5" t="inlineStr"/>
-      <c r="P137" s="5" t="inlineStr"/>
-      <c r="Q137" s="5" t="inlineStr"/>
-      <c r="R137" s="5" t="inlineStr"/>
-      <c r="S137" s="5" t="inlineStr"/>
-      <c r="T137" s="5" t="inlineStr"/>
-      <c r="U137" s="6" t="inlineStr"/>
-      <c r="V137" s="5" t="inlineStr"/>
-      <c r="W137" s="6" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>LBBG1</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>Lake Bonney BESS1</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E138" s="5" t="inlineStr"/>
-      <c r="F138" s="5" t="inlineStr"/>
-      <c r="G138" s="5" t="inlineStr"/>
-      <c r="H138" s="5" t="inlineStr"/>
-      <c r="I138" s="5" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>0.9741</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>1.0022</v>
-      </c>
-      <c r="L138" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="M138" s="5" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="N138" s="5" t="n">
-        <v>0.9841</v>
-      </c>
-      <c r="O138" s="5" t="inlineStr"/>
-      <c r="P138" s="5" t="inlineStr"/>
-      <c r="Q138" s="5" t="inlineStr"/>
-      <c r="R138" s="5" t="inlineStr"/>
-      <c r="S138" s="5" t="inlineStr"/>
-      <c r="T138" s="5" t="inlineStr"/>
-      <c r="U138" s="6" t="inlineStr"/>
-      <c r="V138" s="5" t="inlineStr"/>
-      <c r="W138" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8578,7 +8225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P138"/>
+  <dimension ref="A1:P129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8781,13 +8428,27 @@
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="n">
+        <v>0.8848</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.9045</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.9212</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.9432</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0.8954</v>
+      </c>
       <c r="K4" s="5" t="n">
         <v>0.9092</v>
       </c>
@@ -8932,7 +8593,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -9024,7 +8685,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -9116,14 +8777,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HDWF1</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
+          <t>HDWF2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9918</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0.9799</v>
@@ -9162,11 +8821,15 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HDWF3</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
+          <t>HDWF1</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9965000000000001</v>
+      </c>
       <c r="D13" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -9204,13 +8867,11 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HDWF2</t>
+          <t>HDWF3</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n">
-        <v>0.9918</v>
-      </c>
+      <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -9376,7 +9037,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -9422,7 +9083,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -9692,7 +9353,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -9738,7 +9399,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -10053,13 +9714,27 @@
       </c>
       <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="n">
+        <v>0.9848</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.9772</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.9651999999999999</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0.9653</v>
+      </c>
       <c r="K35" s="5" t="n">
         <v>0.9657</v>
       </c>
@@ -10082,7 +9757,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -10128,7 +9803,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -10447,11 +10122,21 @@
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="5" t="inlineStr"/>
       <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="n">
+        <v>0.9922</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.9741</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>1.0022</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0.9851</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0.979</v>
+      </c>
       <c r="K45" s="5" t="n">
         <v>0.9841</v>
       </c>
@@ -10566,7 +10251,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -10612,7 +10297,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -10810,7 +10495,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
@@ -10856,7 +10541,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -10902,7 +10587,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -10948,7 +10633,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
@@ -11040,7 +10725,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
+          <t>SMFBESS1</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr"/>
@@ -11070,7 +10755,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
+          <t>SMFBESS2</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr"/>
@@ -11130,7 +10815,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr"/>
@@ -11140,31 +10825,29 @@
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="n">
+        <v>0.9966</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>1.0079</v>
+      </c>
       <c r="K62" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="L62" s="5" t="n">
-        <v>1.0102</v>
-      </c>
+      <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="N62" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+      <c r="N62" s="5" t="inlineStr"/>
       <c r="O62" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P62" s="5" t="n">
-        <v>0.9968</v>
-      </c>
+      <c r="P62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr"/>
@@ -11183,15 +10866,21 @@
       <c r="K63" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="L63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="n">
+        <v>1.0102</v>
+      </c>
       <c r="M63" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="N63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="O63" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P63" s="5" t="inlineStr"/>
+      <c r="P63" s="5" t="n">
+        <v>0.9968</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -11236,7 +10925,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT1</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -11282,7 +10971,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -11328,7 +11017,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT1</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -11694,8 +11383,12 @@
       <c r="F75" s="5" t="inlineStr"/>
       <c r="G75" s="5" t="inlineStr"/>
       <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="5" t="inlineStr"/>
+      <c r="I75" s="5" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>0.9996</v>
+      </c>
       <c r="K75" s="5" t="n">
         <v>0.9998</v>
       </c>
@@ -11752,42 +11445,34 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>BARKIPS1</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr"/>
+      <c r="C77" s="5" t="inlineStr"/>
+      <c r="D77" s="5" t="inlineStr"/>
+      <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="J77" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="L77" s="5" t="inlineStr"/>
       <c r="M77" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
       <c r="O77" s="5" t="n">
@@ -11798,34 +11483,42 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>BARKIPS1</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr"/>
-      <c r="C78" s="5" t="inlineStr"/>
-      <c r="D78" s="5" t="inlineStr"/>
-      <c r="E78" s="5" t="inlineStr"/>
+          <t>TORNL1</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="F78" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="J78" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="L78" s="5" t="inlineStr"/>
       <c r="M78" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
       <c r="O78" s="5" t="n">
@@ -11836,7 +11529,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>TORNL1</t>
+          <t>DG_SA1</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -11882,27 +11575,15 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>1.0012</v>
-      </c>
+          <t>BOWWBA1</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr"/>
+      <c r="C80" s="5" t="inlineStr"/>
+      <c r="D80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr"/>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -11915,28 +11596,46 @@
       <c r="K80" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="L80" s="5" t="inlineStr"/>
+      <c r="L80" s="5" t="n">
+        <v>1.0004</v>
+      </c>
       <c r="M80" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="N80" s="5" t="inlineStr"/>
+      <c r="N80" s="5" t="n">
+        <v>0.9999</v>
+      </c>
       <c r="O80" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="P80" s="5" t="inlineStr"/>
+      <c r="P80" s="5" t="n">
+        <v>1.0002</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>BOWWPV1</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr"/>
-      <c r="C81" s="5" t="inlineStr"/>
-      <c r="D81" s="5" t="inlineStr"/>
-      <c r="E81" s="5" t="inlineStr"/>
-      <c r="F81" s="5" t="inlineStr"/>
-      <c r="G81" s="5" t="inlineStr"/>
+          <t>BOLIVAR1</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>1.0012</v>
+      </c>
       <c r="H81" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -11996,7 +11695,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1</t>
+          <t>BOWWPV1</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr"/>
@@ -12005,27 +11704,27 @@
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="5" t="inlineStr"/>
       <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="5" t="inlineStr"/>
+      <c r="H83" s="5" t="n">
+        <v>1.0011</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>1.0002</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>0.9995000000000001</v>
+      </c>
       <c r="K83" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="L83" s="5" t="n">
-        <v>1.0004</v>
-      </c>
+      <c r="L83" s="5" t="inlineStr"/>
       <c r="M83" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="N83" s="5" t="n">
-        <v>0.9999</v>
-      </c>
+      <c r="N83" s="5" t="inlineStr"/>
       <c r="O83" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="P83" s="5" t="n">
-        <v>1.0002</v>
-      </c>
+      <c r="P83" s="5" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -12076,7 +11775,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>DRYCNL</t>
+          <t>WINGF1_1</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -12122,7 +11821,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>WINGF1_1</t>
+          <t>DRYCNL</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -12268,7 +11967,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>HVWWPV1</t>
+          <t>HVWWBA1</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr"/>
@@ -12289,20 +11988,26 @@
       <c r="K90" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="L90" s="5" t="inlineStr"/>
+      <c r="L90" s="5" t="n">
+        <v>1.0043</v>
+      </c>
       <c r="M90" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="N90" s="5" t="inlineStr"/>
+      <c r="N90" s="5" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="O90" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P90" s="5" t="inlineStr"/>
+      <c r="P90" s="5" t="n">
+        <v>1.0022</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1</t>
+          <t>HVWWPV1</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr"/>
@@ -12311,27 +12016,27 @@
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="5" t="inlineStr"/>
       <c r="G91" s="5" t="inlineStr"/>
-      <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr"/>
-      <c r="J91" s="5" t="inlineStr"/>
+      <c r="H91" s="5" t="n">
+        <v>1.0052</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>1.0041</v>
+      </c>
       <c r="K91" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="L91" s="5" t="n">
-        <v>1.0043</v>
-      </c>
+      <c r="L91" s="5" t="inlineStr"/>
       <c r="M91" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="N91" s="5" t="n">
-        <v>1.0024</v>
-      </c>
+      <c r="N91" s="5" t="inlineStr"/>
       <c r="O91" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P91" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="P91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -12382,16 +12087,26 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>ADPPV1</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr"/>
-      <c r="C93" s="5" t="inlineStr"/>
-      <c r="D93" s="5" t="inlineStr"/>
-      <c r="E93" s="5" t="inlineStr"/>
-      <c r="F93" s="5" t="inlineStr"/>
+          <t>PTSTAN1</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>1.0053</v>
+      </c>
       <c r="G93" s="5" t="n">
-        <v>1.0038</v>
+        <v>1.005</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>1.0055</v>
@@ -12418,41 +12133,53 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr"/>
-      <c r="C94" s="5" t="inlineStr"/>
-      <c r="D94" s="5" t="inlineStr"/>
-      <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="5" t="inlineStr"/>
-      <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr"/>
-      <c r="J94" s="5" t="inlineStr"/>
+          <t>STARHLWF</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="K94" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L94" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="L94" s="5" t="inlineStr"/>
       <c r="M94" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N94" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="N94" s="5" t="inlineStr"/>
       <c r="O94" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P94" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="P94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
+          <t>ADPPV2</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr"/>
@@ -12486,15 +12213,27 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr"/>
-      <c r="C96" s="5" t="inlineStr"/>
-      <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="5" t="inlineStr"/>
+          <t>LONSDALE</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>1.005</v>
+      </c>
       <c r="H96" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -12520,27 +12259,15 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C97" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>1.005</v>
-      </c>
+          <t>ADPPV3</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr"/>
+      <c r="C97" s="5" t="inlineStr"/>
+      <c r="D97" s="5" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr"/>
+      <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -12566,7 +12293,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr"/>
@@ -12598,7 +12325,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
+          <t>CBWWPV1</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr"/>
@@ -12630,7 +12357,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG1</t>
+          <t>ADPPV1</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr"/>
@@ -12638,8 +12365,12 @@
       <c r="D100" s="5" t="inlineStr"/>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="5" t="inlineStr"/>
-      <c r="G100" s="5" t="inlineStr"/>
-      <c r="H100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I100" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12662,7 +12393,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
+          <t>ADPBA1</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr"/>
@@ -12670,8 +12401,12 @@
       <c r="D101" s="5" t="inlineStr"/>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr"/>
-      <c r="G101" s="5" t="inlineStr"/>
-      <c r="H101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I101" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12681,20 +12416,26 @@
       <c r="K101" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L101" s="5" t="inlineStr"/>
+      <c r="L101" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="M101" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N101" s="5" t="inlineStr"/>
+      <c r="N101" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="O101" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P101" s="5" t="inlineStr"/>
+      <c r="P101" s="5" t="n">
+        <v>1.0033</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
+          <t>ADPMH1</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr"/>
@@ -12703,32 +12444,32 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="inlineStr"/>
-      <c r="I102" s="5" t="inlineStr"/>
-      <c r="J102" s="5" t="inlineStr"/>
+      <c r="H102" s="5" t="n">
+        <v>1.0055</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>1.0036</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>1.0039</v>
+      </c>
       <c r="K102" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L102" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="L102" s="5" t="inlineStr"/>
       <c r="M102" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N102" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="N102" s="5" t="inlineStr"/>
       <c r="O102" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P102" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="P102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
+          <t>CBWWDG1</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr"/>
@@ -12760,30 +12501,16 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C104" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D104" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+          <t>CBWWBG1</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr"/>
+      <c r="C104" s="5" t="inlineStr"/>
+      <c r="D104" s="5" t="inlineStr"/>
+      <c r="E104" s="5" t="inlineStr"/>
+      <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="5" t="inlineStr"/>
       <c r="I104" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12806,30 +12533,16 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C105" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D105" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E105" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+          <t>CBWWBA1</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr"/>
+      <c r="C105" s="5" t="inlineStr"/>
+      <c r="D105" s="5" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr"/>
+      <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr"/>
       <c r="I105" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12839,20 +12552,26 @@
       <c r="K105" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L105" s="5" t="inlineStr"/>
+      <c r="L105" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="M105" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N105" s="5" t="inlineStr"/>
+      <c r="N105" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="O105" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P105" s="5" t="inlineStr"/>
+      <c r="P105" s="5" t="n">
+        <v>1.0033</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>ADPMH1</t>
+          <t>CBWWDG2</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr"/>
@@ -12861,9 +12580,7 @@
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="5" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -13034,11 +12751,11 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>STANV1</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>1.0111</v>
+        <v>1.0075</v>
       </c>
       <c r="C111" s="5" t="inlineStr"/>
       <c r="D111" s="5" t="inlineStr"/>
@@ -13082,11 +12799,11 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>STANV1</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="C113" s="5" t="inlineStr"/>
       <c r="D113" s="5" t="inlineStr"/>
@@ -13130,11 +12847,11 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0061</v>
       </c>
       <c r="C115" s="5" t="inlineStr"/>
       <c r="D115" s="5" t="inlineStr"/>
@@ -13154,11 +12871,11 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>1.0061</v>
+        <v>1.0111</v>
       </c>
       <c r="C116" s="5" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr"/>
@@ -13228,14 +12945,14 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>NPSNL2</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>0.9826</v>
+        <v>1.0482</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0791</v>
       </c>
       <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="5" t="inlineStr"/>
@@ -13254,14 +12971,14 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr"/>
@@ -13280,14 +12997,14 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="5" t="inlineStr"/>
@@ -13306,14 +13023,14 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>NPSNL2</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
-        <v>1.0482</v>
+        <v>0.9826</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>1.0791</v>
+        <v>1.0098</v>
       </c>
       <c r="D122" s="5" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr"/>
@@ -13332,17 +13049,17 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>TERMSTOR</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0051</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>1.0034</v>
+        <v>1.0047</v>
       </c>
       <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="5" t="inlineStr"/>
@@ -13388,17 +13105,17 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>TERMSTOR</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1.0051</v>
+        <v>1.0037</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>1.0047</v>
+        <v>1.0034</v>
       </c>
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="5" t="inlineStr"/>
@@ -13416,7 +13133,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>TORRA4</t>
+          <t>TORRA2</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
@@ -13450,7 +13167,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>TORRA2</t>
+          <t>TORRA4</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
@@ -13555,294 +13272,8 @@
       <c r="O129" s="5" t="inlineStr"/>
       <c r="P129" s="5" t="inlineStr"/>
     </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>TIBG1</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr"/>
-      <c r="C130" s="5" t="inlineStr"/>
-      <c r="D130" s="5" t="inlineStr"/>
-      <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="5" t="inlineStr"/>
-      <c r="G130" s="5" t="inlineStr"/>
-      <c r="H130" s="5" t="inlineStr"/>
-      <c r="I130" s="5" t="n">
-        <v>1.0001</v>
-      </c>
-      <c r="J130" s="5" t="n">
-        <v>0.9996</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>0.9998</v>
-      </c>
-      <c r="L130" s="5" t="inlineStr"/>
-      <c r="M130" s="5" t="inlineStr"/>
-      <c r="N130" s="5" t="inlineStr"/>
-      <c r="O130" s="5" t="inlineStr"/>
-      <c r="P130" s="5" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>ADPBA1G</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr"/>
-      <c r="C131" s="5" t="inlineStr"/>
-      <c r="D131" s="5" t="inlineStr"/>
-      <c r="E131" s="5" t="inlineStr"/>
-      <c r="F131" s="5" t="inlineStr"/>
-      <c r="G131" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="H131" s="5" t="n">
-        <v>1.0055</v>
-      </c>
-      <c r="I131" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="J131" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>1.0025</v>
-      </c>
-      <c r="L131" s="5" t="inlineStr"/>
-      <c r="M131" s="5" t="inlineStr"/>
-      <c r="N131" s="5" t="inlineStr"/>
-      <c r="O131" s="5" t="inlineStr"/>
-      <c r="P131" s="5" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>BOWWBA1G</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr"/>
-      <c r="C132" s="5" t="inlineStr"/>
-      <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="5" t="inlineStr"/>
-      <c r="F132" s="5" t="inlineStr"/>
-      <c r="G132" s="5" t="inlineStr"/>
-      <c r="H132" s="5" t="n">
-        <v>1.0011</v>
-      </c>
-      <c r="I132" s="5" t="n">
-        <v>1.0002</v>
-      </c>
-      <c r="J132" s="5" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="K132" s="5" t="n">
-        <v>1.0004</v>
-      </c>
-      <c r="L132" s="5" t="inlineStr"/>
-      <c r="M132" s="5" t="inlineStr"/>
-      <c r="N132" s="5" t="inlineStr"/>
-      <c r="O132" s="5" t="inlineStr"/>
-      <c r="P132" s="5" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>CBWWBA1G</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr"/>
-      <c r="C133" s="5" t="inlineStr"/>
-      <c r="D133" s="5" t="inlineStr"/>
-      <c r="E133" s="5" t="inlineStr"/>
-      <c r="F133" s="5" t="inlineStr"/>
-      <c r="G133" s="5" t="inlineStr"/>
-      <c r="H133" s="5" t="inlineStr"/>
-      <c r="I133" s="5" t="n">
-        <v>1.0036</v>
-      </c>
-      <c r="J133" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="K133" s="5" t="n">
-        <v>1.0025</v>
-      </c>
-      <c r="L133" s="5" t="inlineStr"/>
-      <c r="M133" s="5" t="inlineStr"/>
-      <c r="N133" s="5" t="inlineStr"/>
-      <c r="O133" s="5" t="inlineStr"/>
-      <c r="P133" s="5" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>DALNTH01</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr"/>
-      <c r="C134" s="5" t="inlineStr"/>
-      <c r="D134" s="5" t="n">
-        <v>0.8848</v>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>0.9045</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>0.9193</v>
-      </c>
-      <c r="H134" s="5" t="n">
-        <v>0.9212</v>
-      </c>
-      <c r="I134" s="5" t="n">
-        <v>0.9432</v>
-      </c>
-      <c r="J134" s="5" t="n">
-        <v>0.8954</v>
-      </c>
-      <c r="K134" s="5" t="n">
-        <v>0.9092</v>
-      </c>
-      <c r="L134" s="5" t="inlineStr"/>
-      <c r="M134" s="5" t="inlineStr"/>
-      <c r="N134" s="5" t="inlineStr"/>
-      <c r="O134" s="5" t="inlineStr"/>
-      <c r="P134" s="5" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>HPRG1</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr"/>
-      <c r="C135" s="5" t="inlineStr"/>
-      <c r="D135" s="5" t="n">
-        <v>0.9848</v>
-      </c>
-      <c r="E135" s="5" t="n">
-        <v>0.9771</v>
-      </c>
-      <c r="F135" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>0.9838</v>
-      </c>
-      <c r="H135" s="5" t="n">
-        <v>0.9772</v>
-      </c>
-      <c r="I135" s="5" t="n">
-        <v>0.9651999999999999</v>
-      </c>
-      <c r="J135" s="5" t="n">
-        <v>0.9653</v>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>0.9657</v>
-      </c>
-      <c r="L135" s="5" t="inlineStr"/>
-      <c r="M135" s="5" t="inlineStr"/>
-      <c r="N135" s="5" t="inlineStr"/>
-      <c r="O135" s="5" t="inlineStr"/>
-      <c r="P135" s="5" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>HVWWBA1G</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr"/>
-      <c r="C136" s="5" t="inlineStr"/>
-      <c r="D136" s="5" t="inlineStr"/>
-      <c r="E136" s="5" t="inlineStr"/>
-      <c r="F136" s="5" t="inlineStr"/>
-      <c r="G136" s="5" t="inlineStr"/>
-      <c r="H136" s="5" t="n">
-        <v>1.0052</v>
-      </c>
-      <c r="I136" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="J136" s="5" t="n">
-        <v>1.0041</v>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>1.0043</v>
-      </c>
-      <c r="L136" s="5" t="inlineStr"/>
-      <c r="M136" s="5" t="inlineStr"/>
-      <c r="N136" s="5" t="inlineStr"/>
-      <c r="O136" s="5" t="inlineStr"/>
-      <c r="P136" s="5" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>TB2BG1</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr"/>
-      <c r="C137" s="5" t="inlineStr"/>
-      <c r="D137" s="5" t="inlineStr"/>
-      <c r="E137" s="5" t="inlineStr"/>
-      <c r="F137" s="5" t="inlineStr"/>
-      <c r="G137" s="5" t="inlineStr"/>
-      <c r="H137" s="5" t="inlineStr"/>
-      <c r="I137" s="5" t="n">
-        <v>0.9966</v>
-      </c>
-      <c r="J137" s="5" t="n">
-        <v>1.0079</v>
-      </c>
-      <c r="K137" s="5" t="n">
-        <v>1.0102</v>
-      </c>
-      <c r="L137" s="5" t="inlineStr"/>
-      <c r="M137" s="5" t="inlineStr"/>
-      <c r="N137" s="5" t="inlineStr"/>
-      <c r="O137" s="5" t="inlineStr"/>
-      <c r="P137" s="5" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>LBBG1</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr"/>
-      <c r="C138" s="5" t="inlineStr"/>
-      <c r="D138" s="5" t="inlineStr"/>
-      <c r="E138" s="5" t="inlineStr"/>
-      <c r="F138" s="5" t="n">
-        <v>0.9922</v>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>0.9741</v>
-      </c>
-      <c r="H138" s="5" t="n">
-        <v>1.0022</v>
-      </c>
-      <c r="I138" s="5" t="n">
-        <v>0.9851</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>0.9841</v>
-      </c>
-      <c r="L138" s="5" t="inlineStr"/>
-      <c r="M138" s="5" t="inlineStr"/>
-      <c r="N138" s="5" t="inlineStr"/>
-      <c r="O138" s="5" t="inlineStr"/>
-      <c r="P138" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B138">
+  <conditionalFormatting sqref="B2:B129">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -13854,7 +13285,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C138">
+  <conditionalFormatting sqref="C2:C129">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -13866,7 +13297,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D138">
+  <conditionalFormatting sqref="D2:D129">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -13878,7 +13309,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E138">
+  <conditionalFormatting sqref="E2:E129">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -13890,7 +13321,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F138">
+  <conditionalFormatting sqref="F2:F129">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -13902,7 +13333,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G138">
+  <conditionalFormatting sqref="G2:G129">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -13914,7 +13345,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H138">
+  <conditionalFormatting sqref="H2:H129">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -13926,7 +13357,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I138">
+  <conditionalFormatting sqref="I2:I129">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -13938,7 +13369,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J138">
+  <conditionalFormatting sqref="J2:J129">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -13950,7 +13381,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K138">
+  <conditionalFormatting sqref="K2:K129">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -13962,7 +13393,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L138">
+  <conditionalFormatting sqref="M2:M129">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -13974,44 +13405,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M138">
+  <conditionalFormatting sqref="O2:O129">
     <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N138">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O138">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P138">
-    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -14468,12 +13863,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
+          <t>SMFBESS1</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 2</t>
+          <t>Summerfield BESS 1</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -14497,12 +13892,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
+          <t>SMFBESS2</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 1</t>
+          <t>Summerfield BESS 2</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -14715,7 +14110,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -14744,7 +14139,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -14889,12 +14284,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -14947,12 +14342,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -15092,7 +14487,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -15102,7 +14497,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -15121,7 +14516,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -15131,7 +14526,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">

--- a/outputs/SA_mlf.xlsx
+++ b/outputs/SA_mlf.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MLF Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Biggest Movers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1005,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>80.5</v>
+        <v>39</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>0.9352</v>
@@ -1139,12 +1139,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>39</v>
+        <v>80.5</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>0.9352</v>
@@ -1273,12 +1273,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HDWF2</t>
+          <t>HDWF1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 2</t>
+          <t>Hornsdale Wind Farm</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1289,9 +1289,11 @@
       <c r="D12" s="4" t="n">
         <v>102.4</v>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
       <c r="F12" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0.9799</v>
@@ -1338,12 +1340,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HDWF1</t>
+          <t>HDWF3</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm</t>
+          <t>Hornsdale Wind Farm 3</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1352,14 +1354,10 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.9965000000000001</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -1405,12 +1403,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HDWF3</t>
+          <t>HDWF2</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Hornsdale Wind Farm 3</t>
+          <t>Hornsdale Wind Farm 2</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1419,10 +1417,12 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>112</v>
+        <v>102.4</v>
       </c>
       <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>0.9918</v>
+      </c>
       <c r="G14" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -1659,7 +1659,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2122,21 +2122,21 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Hallett 1 Wind Farm</t>
+          <t>Hallett Power Station</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>94.5</v>
+        <v>217</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0.9835</v>
@@ -2189,21 +2189,21 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Hallett Power Station</t>
+          <t>Hallett 1 Wind Farm</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>217</v>
+        <v>94.5</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0.9835</v>
@@ -2773,12 +2773,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Snowtown Wind Farm Stage 2 North</t>
+          <t>Snowtown South Wind Farm</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>0.9782</v>
@@ -2840,12 +2840,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Snowtown South Wind Farm</t>
+          <t>Snowtown Wind Farm Stage 2 North</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>0.9782</v>
@@ -3523,7 +3523,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3893,7 +3893,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3960,7 +3960,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0.9932</v>
@@ -4027,7 +4027,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>0.9932</v>
@@ -4094,7 +4094,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0.9932</v>
@@ -4228,12 +4228,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
+          <t>SMFBESS2</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 1</t>
+          <t>Summerfield BESS 2</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -4283,12 +4283,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
+          <t>SMFBESS1</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 2</t>
+          <t>Summerfield BESS 1</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -4389,7 +4389,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4399,11 +4399,11 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="5" t="inlineStr"/>
@@ -4421,28 +4421,38 @@
       <c r="N62" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="O62" s="5" t="inlineStr"/>
+      <c r="O62" s="5" t="n">
+        <v>1.0102</v>
+      </c>
       <c r="P62" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="Q62" s="5" t="inlineStr"/>
+      <c r="Q62" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="R62" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="S62" s="5" t="inlineStr"/>
+      <c r="S62" s="5" t="n">
+        <v>0.9968</v>
+      </c>
       <c r="T62" s="5" t="n">
         <v>0.0023</v>
       </c>
       <c r="U62" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="V62" s="5" t="inlineStr"/>
-      <c r="W62" s="6" t="inlineStr"/>
+      <c r="V62" s="5" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="W62" s="6" t="n">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4452,11 +4462,11 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="5" t="inlineStr"/>
@@ -4474,33 +4484,23 @@
       <c r="N63" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="O63" s="5" t="n">
-        <v>1.0102</v>
-      </c>
+      <c r="O63" s="5" t="inlineStr"/>
       <c r="P63" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="Q63" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+      <c r="Q63" s="5" t="inlineStr"/>
       <c r="R63" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="S63" s="5" t="n">
-        <v>0.9968</v>
-      </c>
+      <c r="S63" s="5" t="inlineStr"/>
       <c r="T63" s="5" t="n">
         <v>0.0023</v>
       </c>
       <c r="U63" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="V63" s="5" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="W63" s="6" t="n">
-        <v>0.23</v>
-      </c>
+      <c r="V63" s="5" t="inlineStr"/>
+      <c r="W63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -4566,7 +4566,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT1</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4700,7 +4700,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT1</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5338,47 +5338,53 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>BARKIPS1</t>
+          <t>DG_SA1</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Barker Inlet Power Station</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
+          <t>SA1 Dummy Generator</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v/>
       </c>
       <c r="D77" s="4" t="n">
-        <v>211</v>
-      </c>
-      <c r="E77" s="5" t="inlineStr"/>
-      <c r="F77" s="5" t="inlineStr"/>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I77" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="O77" s="5" t="inlineStr"/>
       <c r="P77" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="Q77" s="5" t="inlineStr"/>
       <c r="R77" s="5" t="n">
@@ -5386,10 +5392,10 @@
       </c>
       <c r="S77" s="5" t="inlineStr"/>
       <c r="T77" s="5" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="U77" s="6" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="V77" s="5" t="inlineStr"/>
       <c r="W77" s="6" t="inlineStr"/>
@@ -5397,12 +5403,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>TORNL1</t>
+          <t>BARKIPS1</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>TORRENS ISLAND POWER STATION</t>
+          <t>Barker Inlet Power Station</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5411,41 +5417,33 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr"/>
+      <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="M78" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="O78" s="5" t="inlineStr"/>
       <c r="P78" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="Q78" s="5" t="inlineStr"/>
       <c r="R78" s="5" t="n">
@@ -5453,10 +5451,10 @@
       </c>
       <c r="S78" s="5" t="inlineStr"/>
       <c r="T78" s="5" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="U78" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="V78" s="5" t="inlineStr"/>
       <c r="W78" s="6" t="inlineStr"/>
@@ -5464,17 +5462,21 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
+          <t>TORNL1</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>SA1 Dummy Generator</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="n"/>
+          <t>TORRENS ISLAND POWER STATION</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Fossil</t>
+        </is>
+      </c>
       <c r="D79" s="4" t="n">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="E79" s="5" t="n">
         <v>1</v>
@@ -5527,7 +5529,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1</t>
+          <t>BOLIVAR1</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -5537,18 +5539,30 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr"/>
-      <c r="J80" s="5" t="inlineStr"/>
+        <v>9.9</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>1.0012</v>
+      </c>
       <c r="K80" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -5561,38 +5575,28 @@
       <c r="N80" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="O80" s="5" t="n">
-        <v>1.0004</v>
-      </c>
+      <c r="O80" s="5" t="inlineStr"/>
       <c r="P80" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="Q80" s="5" t="n">
-        <v>0.9999</v>
-      </c>
+      <c r="Q80" s="5" t="inlineStr"/>
       <c r="R80" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="S80" s="5" t="n">
-        <v>1.0002</v>
-      </c>
+      <c r="S80" s="5" t="inlineStr"/>
       <c r="T80" s="5" t="n">
         <v>0.0003</v>
       </c>
       <c r="U80" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V80" s="5" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="W80" s="6" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="V80" s="5" t="inlineStr"/>
+      <c r="W80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
+          <t>BOWWPV1</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -5602,30 +5606,18 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>1.0012</v>
-      </c>
+        <v>8.25</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr"/>
       <c r="K81" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -5714,7 +5706,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>BOWWPV1</t>
+          <t>BOWWBA1</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5724,11 +5716,11 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>8.25</v>
+        <v>3</v>
       </c>
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="5" t="inlineStr"/>
@@ -5748,23 +5740,33 @@
       <c r="N83" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="O83" s="5" t="inlineStr"/>
+      <c r="O83" s="5" t="n">
+        <v>1.0004</v>
+      </c>
       <c r="P83" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="Q83" s="5" t="inlineStr"/>
+      <c r="Q83" s="5" t="n">
+        <v>0.9999</v>
+      </c>
       <c r="R83" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="S83" s="5" t="inlineStr"/>
+      <c r="S83" s="5" t="n">
+        <v>1.0002</v>
+      </c>
       <c r="T83" s="5" t="n">
         <v>0.0003</v>
       </c>
       <c r="U83" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V83" s="5" t="inlineStr"/>
-      <c r="W83" s="6" t="inlineStr"/>
+      <c r="V83" s="5" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="W83" s="6" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -5836,21 +5838,21 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>WINGF1_1</t>
+          <t>DRYCNL</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Wingfield 1 Landfill Gas Power Station</t>
+          <t>Dry Creek Gas Turbine Station</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D85" s="4" t="n">
-        <v>4.12</v>
+        <v>50</v>
       </c>
       <c r="E85" s="5" t="n">
         <v>1.0029</v>
@@ -5903,21 +5905,21 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>DRYCNL</t>
+          <t>WINGF1_1</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Dry Creek Gas Turbine Station</t>
+          <t>Wingfield 1 Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>50</v>
+        <v>4.12</v>
       </c>
       <c r="E86" s="5" t="n">
         <v>1.0029</v>
@@ -6133,7 +6135,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1</t>
+          <t>HVWWPV1</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -6143,11 +6145,11 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E90" s="5" t="inlineStr"/>
       <c r="F90" s="5" t="inlineStr"/>
@@ -6167,38 +6169,28 @@
       <c r="N90" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="O90" s="5" t="n">
-        <v>1.0043</v>
-      </c>
+      <c r="O90" s="5" t="inlineStr"/>
       <c r="P90" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="Q90" s="5" t="n">
-        <v>1.0024</v>
-      </c>
+      <c r="Q90" s="5" t="inlineStr"/>
       <c r="R90" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="S90" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="S90" s="5" t="inlineStr"/>
       <c r="T90" s="5" t="n">
         <v>-0.0002</v>
       </c>
       <c r="U90" s="6" t="n">
         <v>-0.02</v>
       </c>
-      <c r="V90" s="5" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="W90" s="6" t="n">
-        <v>-0.02</v>
-      </c>
+      <c r="V90" s="5" t="inlineStr"/>
+      <c r="W90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>HVWWPV1</t>
+          <t>HVWWBA1</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -6208,11 +6200,11 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="5" t="inlineStr"/>
@@ -6232,23 +6224,33 @@
       <c r="N91" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="O91" s="5" t="inlineStr"/>
+      <c r="O91" s="5" t="n">
+        <v>1.0043</v>
+      </c>
       <c r="P91" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="Q91" s="5" t="inlineStr"/>
+      <c r="Q91" s="5" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="R91" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="S91" s="5" t="inlineStr"/>
+      <c r="S91" s="5" t="n">
+        <v>1.0022</v>
+      </c>
       <c r="T91" s="5" t="n">
         <v>-0.0002</v>
       </c>
       <c r="U91" s="6" t="n">
         <v>-0.02</v>
       </c>
-      <c r="V91" s="5" t="inlineStr"/>
-      <c r="W91" s="6" t="inlineStr"/>
+      <c r="V91" s="5" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="W91" s="6" t="n">
+        <v>-0.02</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -6320,39 +6322,29 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
+          <t>ADPPV1</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>1.0053</v>
-      </c>
+        <v>24.75</v>
+      </c>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="5" t="inlineStr"/>
+      <c r="H93" s="5" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="5" t="n">
-        <v>1.005</v>
+        <v>1.0038</v>
       </c>
       <c r="K93" s="5" t="n">
         <v>1.0055</v>
@@ -6387,39 +6379,29 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
+          <t>ADPBA1</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Starfish Hill Wind Farm</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>1.0053</v>
-      </c>
+        <v>7.76</v>
+      </c>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="5" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="5" t="n">
-        <v>1.005</v>
+        <v>1.0038</v>
       </c>
       <c r="K94" s="5" t="n">
         <v>1.0055</v>
@@ -6433,28 +6415,38 @@
       <c r="N94" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O94" s="5" t="inlineStr"/>
+      <c r="O94" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="P94" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q94" s="5" t="inlineStr"/>
+      <c r="Q94" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="R94" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S94" s="5" t="inlineStr"/>
+      <c r="S94" s="5" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="T94" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U94" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V94" s="5" t="inlineStr"/>
-      <c r="W94" s="6" t="inlineStr"/>
+      <c r="V94" s="5" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="W94" s="6" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
+          <t>ADPPV3</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -6468,7 +6460,7 @@
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="5" t="inlineStr"/>
@@ -6509,40 +6501,28 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
+          <t>ADPPV2</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Lonsdale Power Station</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="I96" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="J96" s="5" t="n">
-        <v>1.005</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="E96" s="5" t="inlineStr"/>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
+      <c r="H96" s="5" t="inlineStr"/>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="5" t="inlineStr"/>
       <c r="K96" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -6576,28 +6556,40 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
+          <t>STARHLWF</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Starfish Hill Wind Farm</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Wind</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr"/>
-      <c r="J97" s="5" t="inlineStr"/>
+        <v>34.5</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>1.005</v>
+      </c>
       <c r="K97" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -6631,7 +6623,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
+          <t>CBWWPV1</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -6645,7 +6637,7 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>1.08</v>
+        <v>2.75</v>
       </c>
       <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="5" t="inlineStr"/>
@@ -6684,7 +6676,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
+          <t>CBWWDG2</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -6694,11 +6686,11 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>2.75</v>
+        <v>0.72</v>
       </c>
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="5" t="inlineStr"/>
@@ -6737,33 +6729,29 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>ADPPV1</t>
+          <t>CBWWDG1</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>24.75</v>
+        <v>2</v>
       </c>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="5" t="inlineStr"/>
       <c r="G100" s="5" t="inlineStr"/>
       <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="inlineStr"/>
-      <c r="J100" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="J100" s="5" t="inlineStr"/>
+      <c r="K100" s="5" t="inlineStr"/>
       <c r="L100" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6794,33 +6782,29 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
+          <t>CBWWBG1</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>7.76</v>
+        <v>0.664</v>
       </c>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr"/>
       <c r="G101" s="5" t="inlineStr"/>
       <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="inlineStr"/>
-      <c r="J101" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="K101" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="J101" s="5" t="inlineStr"/>
+      <c r="K101" s="5" t="inlineStr"/>
       <c r="L101" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6830,52 +6814,42 @@
       <c r="N101" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O101" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="O101" s="5" t="inlineStr"/>
       <c r="P101" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q101" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="Q101" s="5" t="inlineStr"/>
       <c r="R101" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S101" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="S101" s="5" t="inlineStr"/>
       <c r="T101" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U101" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V101" s="5" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="W101" s="6" t="n">
-        <v>-0.04</v>
-      </c>
+      <c r="V101" s="5" t="inlineStr"/>
+      <c r="W101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>ADPMH1</t>
+          <t>CBWWBA1</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Adelaide Desalination Plant</t>
+          <t>Christies Beach Wastewater Treatment Plant</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="5" t="inlineStr"/>
@@ -6883,9 +6857,7 @@
       <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="5" t="inlineStr"/>
-      <c r="K102" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="K102" s="5" t="inlineStr"/>
       <c r="L102" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -6895,28 +6867,38 @@
       <c r="N102" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O102" s="5" t="inlineStr"/>
+      <c r="O102" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="P102" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q102" s="5" t="inlineStr"/>
+      <c r="Q102" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="R102" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S102" s="5" t="inlineStr"/>
+      <c r="S102" s="5" t="n">
+        <v>1.0033</v>
+      </c>
       <c r="T102" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U102" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V102" s="5" t="inlineStr"/>
-      <c r="W102" s="6" t="inlineStr"/>
+      <c r="V102" s="5" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="W102" s="6" t="n">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG1</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -6926,11 +6908,11 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="5" t="inlineStr"/>
@@ -6969,29 +6951,43 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
+          <t>PTSTAN1</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Pt Stanvac Power Station</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.664</v>
-      </c>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr"/>
-      <c r="J104" s="5" t="inlineStr"/>
-      <c r="K104" s="5" t="inlineStr"/>
+        <v>57.6</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L104" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -7022,29 +7018,43 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
+          <t>LONSDALE</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Lonsdale Power Station</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E105" s="5" t="inlineStr"/>
-      <c r="F105" s="5" t="inlineStr"/>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr"/>
-      <c r="I105" s="5" t="inlineStr"/>
-      <c r="J105" s="5" t="inlineStr"/>
-      <c r="K105" s="5" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L105" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -7054,52 +7064,42 @@
       <c r="N105" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="O105" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="O105" s="5" t="inlineStr"/>
       <c r="P105" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="Q105" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="Q105" s="5" t="inlineStr"/>
       <c r="R105" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="S105" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="S105" s="5" t="inlineStr"/>
       <c r="T105" s="5" t="n">
         <v>-0.0004</v>
       </c>
       <c r="U105" s="6" t="n">
         <v>-0.04</v>
       </c>
-      <c r="V105" s="5" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="W105" s="6" t="n">
-        <v>-0.04</v>
-      </c>
+      <c r="V105" s="5" t="inlineStr"/>
+      <c r="W105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
+          <t>ADPMH1</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Christies Beach Wastewater Treatment Plant</t>
+          <t>Adelaide Desalination Plant</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0.72</v>
+        <v>1.44</v>
       </c>
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="5" t="inlineStr"/>
@@ -7107,7 +7107,9 @@
       <c r="H106" s="5" t="inlineStr"/>
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="5" t="inlineStr"/>
-      <c r="K106" s="5" t="inlineStr"/>
+      <c r="K106" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="L106" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -7370,12 +7372,12 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>STANV1</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Pt Stanvac Power Station</t>
+          <t>Amcor Glass, Gawler Plant</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -7384,10 +7386,10 @@
         </is>
       </c>
       <c r="D111" s="4" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0111</v>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
       <c r="G111" s="5" t="inlineStr"/>
@@ -7452,24 +7454,24 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>STANV1</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Tea Tree Gully Landfill Gas Power Station</t>
+          <t>Pt Stanvac Power Station</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Fossil</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
       <c r="G113" s="5" t="inlineStr"/>
@@ -7534,24 +7536,24 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>ANGASTON POWER STATION</t>
+          <t>Tea Tree Gully Landfill Gas Power Station</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Fossil</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1.0061</v>
+        <v>1.0042</v>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
       <c r="G115" s="5" t="inlineStr"/>
@@ -7575,12 +7577,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Amcor Glass, Gawler Plant</t>
+          <t>ANGASTON POWER STATION</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -7589,10 +7591,10 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1.0111</v>
+        <v>1.0061</v>
       </c>
       <c r="F116" s="5" t="inlineStr"/>
       <c r="G116" s="5" t="inlineStr"/>
@@ -7700,7 +7702,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>NPSNL2</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -7714,13 +7716,13 @@
         </is>
       </c>
       <c r="D119" s="4" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1.0482</v>
+        <v>0.9826</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>1.0791</v>
+        <v>1.0098</v>
       </c>
       <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="5" t="inlineStr"/>
@@ -7743,7 +7745,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -7757,13 +7759,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>100</v>
+        <v>265</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="G120" s="5" t="inlineStr"/>
       <c r="H120" s="5" t="inlineStr"/>
@@ -7786,7 +7788,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -7800,13 +7802,13 @@
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="G121" s="5" t="inlineStr"/>
       <c r="H121" s="5" t="inlineStr"/>
@@ -7829,7 +7831,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL2</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -7843,13 +7845,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.9826</v>
+        <v>1.0482</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0791</v>
       </c>
       <c r="G122" s="5" t="inlineStr"/>
       <c r="H122" s="5" t="inlineStr"/>
@@ -7872,30 +7874,30 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>TERMSTOR</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
+          <t>Terminal Storage Mini Hydro Power Station</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Other Renewable</t>
+          <t>Hydro</t>
         </is>
       </c>
       <c r="D123" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>1.0051</v>
+        <v>1.0037</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.0047</v>
+        <v>1.0034</v>
       </c>
       <c r="H123" s="5" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr"/>
@@ -7962,30 +7964,30 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>TERMSTOR</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Terminal Storage Mini Hydro Power Station</t>
+          <t>Pedler Creek Landfill Gas Power Station Units 1-3</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Hydro</t>
+          <t>Other Renewable</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0051</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>1.0034</v>
+        <v>1.0047</v>
       </c>
       <c r="H125" s="5" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr"/>
@@ -8007,7 +8009,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>TORRA2</t>
+          <t>TORRA4</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -8058,7 +8060,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>TORRA4</t>
+          <t>TORRA2</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -8593,7 +8595,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -8685,7 +8687,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -8777,12 +8779,14 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HDWF2</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr"/>
+          <t>HDWF1</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0.9792999999999999</v>
+      </c>
       <c r="C12" s="5" t="n">
-        <v>0.9918</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0.9799</v>
@@ -8821,15 +8825,11 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>HDWF1</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>0.9792999999999999</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>0.9965000000000001</v>
-      </c>
+          <t>HDWF3</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -8867,11 +8867,13 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HDWF3</t>
+          <t>HDWF2</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="n">
+        <v>0.9918</v>
+      </c>
       <c r="D14" s="5" t="n">
         <v>0.9799</v>
       </c>
@@ -9037,7 +9039,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>SNUG2</t>
+          <t>SNUG3</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
@@ -9083,7 +9085,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SNUG3</t>
+          <t>SNUG2</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
@@ -9353,7 +9355,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>HALLWF1</t>
+          <t>AGLHAL</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
@@ -9399,7 +9401,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>AGLHAL</t>
+          <t>HALLWF1</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -9757,7 +9759,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SNOWNTH1</t>
+          <t>SNOWSTH1</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -9803,7 +9805,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SNOWSTH1</t>
+          <t>SNOWNTH1</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -10251,7 +10253,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -10297,7 +10299,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -10495,7 +10497,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>QPS2</t>
+          <t>QPS3</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
@@ -10541,7 +10543,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>QPS1</t>
+          <t>QPS2</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -10587,7 +10589,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>QPS5</t>
+          <t>QPS1</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
@@ -10633,7 +10635,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>QPS3</t>
+          <t>QPS5</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
@@ -10725,7 +10727,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
+          <t>SMFBESS2</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr"/>
@@ -10755,7 +10757,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
+          <t>SMFBESS1</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr"/>
@@ -10815,7 +10817,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr"/>
@@ -10834,20 +10836,26 @@
       <c r="K62" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="L62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="n">
+        <v>1.0102</v>
+      </c>
       <c r="M62" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="N62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="n">
+        <v>0.9945000000000001</v>
+      </c>
       <c r="O62" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P62" s="5" t="inlineStr"/>
+      <c r="P62" s="5" t="n">
+        <v>0.9968</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr"/>
@@ -10866,21 +10874,15 @@
       <c r="K63" s="5" t="n">
         <v>1.0102</v>
       </c>
-      <c r="L63" s="5" t="n">
-        <v>1.0102</v>
-      </c>
+      <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="n">
         <v>0.9945000000000001</v>
       </c>
-      <c r="N63" s="5" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+      <c r="N63" s="5" t="inlineStr"/>
       <c r="O63" s="5" t="n">
         <v>0.9968</v>
       </c>
-      <c r="P63" s="5" t="n">
-        <v>0.9968</v>
-      </c>
+      <c r="P63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -10925,7 +10927,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT3</t>
+          <t>DRYCGT1</t>
         </is>
       </c>
       <c r="B65" s="5" t="n">
@@ -10971,7 +10973,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT2</t>
+          <t>DRYCGT3</t>
         </is>
       </c>
       <c r="B66" s="5" t="n">
@@ -11017,7 +11019,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>DRYCGT1</t>
+          <t>DRYCGT2</t>
         </is>
       </c>
       <c r="B67" s="5" t="n">
@@ -11445,34 +11447,42 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>BARKIPS1</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr"/>
-      <c r="C77" s="5" t="inlineStr"/>
-      <c r="D77" s="5" t="inlineStr"/>
-      <c r="E77" s="5" t="inlineStr"/>
+          <t>DG_SA1</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="F77" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="J77" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="L77" s="5" t="inlineStr"/>
       <c r="M77" s="5" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
       <c r="O77" s="5" t="n">
@@ -11483,42 +11493,34 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>TORNL1</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>BARKIPS1</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr"/>
+      <c r="C78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="J78" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>1</v>
+        <v>1.0001</v>
       </c>
       <c r="L78" s="5" t="inlineStr"/>
       <c r="M78" s="5" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
       <c r="O78" s="5" t="n">
@@ -11529,7 +11531,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>DG_SA1</t>
+          <t>TORNL1</t>
         </is>
       </c>
       <c r="B79" s="5" t="n">
@@ -11575,15 +11577,27 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>BOWWBA1</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr"/>
-      <c r="C80" s="5" t="inlineStr"/>
-      <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr"/>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr"/>
+          <t>BOLIVAR1</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>1.0045</v>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>1.0054</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>1.0039</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>1.0016</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1.0012</v>
+      </c>
       <c r="H80" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -11596,46 +11610,28 @@
       <c r="K80" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="L80" s="5" t="n">
-        <v>1.0004</v>
-      </c>
+      <c r="L80" s="5" t="inlineStr"/>
       <c r="M80" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="N80" s="5" t="n">
-        <v>0.9999</v>
-      </c>
+      <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="P80" s="5" t="n">
-        <v>1.0002</v>
-      </c>
+      <c r="P80" s="5" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>BOLIVAR1</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>1.0045</v>
-      </c>
-      <c r="C81" s="5" t="n">
-        <v>1.0054</v>
-      </c>
-      <c r="D81" s="5" t="n">
-        <v>1.0039</v>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>1.0016</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>1.0012</v>
-      </c>
+          <t>BOWWPV1</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr"/>
+      <c r="C81" s="5" t="inlineStr"/>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
       <c r="H81" s="5" t="n">
         <v>1.0011</v>
       </c>
@@ -11695,7 +11691,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>BOWWPV1</t>
+          <t>BOWWBA1</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr"/>
@@ -11716,15 +11712,21 @@
       <c r="K83" s="5" t="n">
         <v>1.0004</v>
       </c>
-      <c r="L83" s="5" t="inlineStr"/>
+      <c r="L83" s="5" t="n">
+        <v>1.0004</v>
+      </c>
       <c r="M83" s="5" t="n">
         <v>0.9999</v>
       </c>
-      <c r="N83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="n">
+        <v>0.9999</v>
+      </c>
       <c r="O83" s="5" t="n">
         <v>1.0002</v>
       </c>
-      <c r="P83" s="5" t="inlineStr"/>
+      <c r="P83" s="5" t="n">
+        <v>1.0002</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -11775,7 +11777,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>WINGF1_1</t>
+          <t>DRYCNL</t>
         </is>
       </c>
       <c r="B85" s="5" t="n">
@@ -11821,7 +11823,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>DRYCNL</t>
+          <t>WINGF1_1</t>
         </is>
       </c>
       <c r="B86" s="5" t="n">
@@ -11967,7 +11969,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>HVWWBA1</t>
+          <t>HVWWPV1</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr"/>
@@ -11988,26 +11990,20 @@
       <c r="K90" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="L90" s="5" t="n">
-        <v>1.0043</v>
-      </c>
+      <c r="L90" s="5" t="inlineStr"/>
       <c r="M90" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="N90" s="5" t="n">
-        <v>1.0024</v>
-      </c>
+      <c r="N90" s="5" t="inlineStr"/>
       <c r="O90" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P90" s="5" t="n">
-        <v>1.0022</v>
-      </c>
+      <c r="P90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>HVWWPV1</t>
+          <t>HVWWBA1</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr"/>
@@ -12028,15 +12024,21 @@
       <c r="K91" s="5" t="n">
         <v>1.0043</v>
       </c>
-      <c r="L91" s="5" t="inlineStr"/>
+      <c r="L91" s="5" t="n">
+        <v>1.0043</v>
+      </c>
       <c r="M91" s="5" t="n">
         <v>1.0024</v>
       </c>
-      <c r="N91" s="5" t="inlineStr"/>
+      <c r="N91" s="5" t="n">
+        <v>1.0024</v>
+      </c>
       <c r="O91" s="5" t="n">
         <v>1.0022</v>
       </c>
-      <c r="P91" s="5" t="inlineStr"/>
+      <c r="P91" s="5" t="n">
+        <v>1.0022</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -12087,26 +12089,16 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>PTSTAN1</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C93" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>1.0053</v>
-      </c>
+          <t>ADPPV1</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr"/>
+      <c r="C93" s="5" t="inlineStr"/>
+      <c r="D93" s="5" t="inlineStr"/>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="5" t="inlineStr"/>
       <c r="G93" s="5" t="n">
-        <v>1.005</v>
+        <v>1.0038</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>1.0055</v>
@@ -12133,26 +12125,16 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>STARHLWF</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C94" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>1.0053</v>
-      </c>
+          <t>ADPBA1</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr"/>
+      <c r="C94" s="5" t="inlineStr"/>
+      <c r="D94" s="5" t="inlineStr"/>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="5" t="inlineStr"/>
       <c r="G94" s="5" t="n">
-        <v>1.005</v>
+        <v>1.0038</v>
       </c>
       <c r="H94" s="5" t="n">
         <v>1.0055</v>
@@ -12166,20 +12148,26 @@
       <c r="K94" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L94" s="5" t="inlineStr"/>
+      <c r="L94" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="M94" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N94" s="5" t="inlineStr"/>
+      <c r="N94" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="O94" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P94" s="5" t="inlineStr"/>
+      <c r="P94" s="5" t="n">
+        <v>1.0033</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>ADPPV2</t>
+          <t>ADPPV3</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr"/>
@@ -12213,27 +12201,15 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>LONSDALE</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>1.0051</v>
-      </c>
-      <c r="D96" s="5" t="n">
-        <v>1.0047</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>1.0053</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>1.005</v>
-      </c>
+          <t>ADPPV2</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr"/>
+      <c r="C96" s="5" t="inlineStr"/>
+      <c r="D96" s="5" t="inlineStr"/>
+      <c r="E96" s="5" t="inlineStr"/>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr"/>
       <c r="H96" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -12259,15 +12235,27 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>ADPPV3</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr"/>
-      <c r="C97" s="5" t="inlineStr"/>
-      <c r="D97" s="5" t="inlineStr"/>
-      <c r="E97" s="5" t="inlineStr"/>
-      <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="5" t="inlineStr"/>
+          <t>STARHLWF</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>1.005</v>
+      </c>
       <c r="H97" s="5" t="n">
         <v>1.0055</v>
       </c>
@@ -12293,7 +12281,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV2</t>
+          <t>CBWWPV1</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr"/>
@@ -12325,7 +12313,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>CBWWPV1</t>
+          <t>CBWWDG2</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr"/>
@@ -12357,7 +12345,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>ADPPV1</t>
+          <t>CBWWDG1</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr"/>
@@ -12365,12 +12353,8 @@
       <c r="D100" s="5" t="inlineStr"/>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="5" t="inlineStr"/>
-      <c r="G100" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="G100" s="5" t="inlineStr"/>
+      <c r="H100" s="5" t="inlineStr"/>
       <c r="I100" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12393,7 +12377,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>ADPBA1</t>
+          <t>CBWWBG1</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr"/>
@@ -12401,12 +12385,8 @@
       <c r="D101" s="5" t="inlineStr"/>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="5" t="inlineStr"/>
-      <c r="G101" s="5" t="n">
-        <v>1.0038</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="G101" s="5" t="inlineStr"/>
+      <c r="H101" s="5" t="inlineStr"/>
       <c r="I101" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12416,26 +12396,20 @@
       <c r="K101" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L101" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="L101" s="5" t="inlineStr"/>
       <c r="M101" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N101" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="N101" s="5" t="inlineStr"/>
       <c r="O101" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P101" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="P101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>ADPMH1</t>
+          <t>CBWWBA1</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr"/>
@@ -12444,9 +12418,7 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="5" t="inlineStr"/>
       <c r="G102" s="5" t="inlineStr"/>
-      <c r="H102" s="5" t="n">
-        <v>1.0055</v>
-      </c>
+      <c r="H102" s="5" t="inlineStr"/>
       <c r="I102" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12456,20 +12428,26 @@
       <c r="K102" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L102" s="5" t="inlineStr"/>
+      <c r="L102" s="5" t="n">
+        <v>1.0025</v>
+      </c>
       <c r="M102" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N102" s="5" t="inlineStr"/>
+      <c r="N102" s="5" t="n">
+        <v>1.0037</v>
+      </c>
       <c r="O102" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P102" s="5" t="inlineStr"/>
+      <c r="P102" s="5" t="n">
+        <v>1.0033</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG1</t>
+          <t>CBWWPV2</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr"/>
@@ -12501,16 +12479,30 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>CBWWBG1</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr"/>
-      <c r="C104" s="5" t="inlineStr"/>
-      <c r="D104" s="5" t="inlineStr"/>
-      <c r="E104" s="5" t="inlineStr"/>
-      <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="5" t="inlineStr"/>
-      <c r="H104" s="5" t="inlineStr"/>
+          <t>PTSTAN1</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I104" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12533,16 +12525,30 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>CBWWBA1</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr"/>
-      <c r="C105" s="5" t="inlineStr"/>
-      <c r="D105" s="5" t="inlineStr"/>
-      <c r="E105" s="5" t="inlineStr"/>
-      <c r="F105" s="5" t="inlineStr"/>
-      <c r="G105" s="5" t="inlineStr"/>
-      <c r="H105" s="5" t="inlineStr"/>
+          <t>LONSDALE</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>1.0075</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>1.0051</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>1.0047</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>1.0068</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>1.0053</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I105" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12552,26 +12558,20 @@
       <c r="K105" s="5" t="n">
         <v>1.0025</v>
       </c>
-      <c r="L105" s="5" t="n">
-        <v>1.0025</v>
-      </c>
+      <c r="L105" s="5" t="inlineStr"/>
       <c r="M105" s="5" t="n">
         <v>1.0037</v>
       </c>
-      <c r="N105" s="5" t="n">
-        <v>1.0037</v>
-      </c>
+      <c r="N105" s="5" t="inlineStr"/>
       <c r="O105" s="5" t="n">
         <v>1.0033</v>
       </c>
-      <c r="P105" s="5" t="n">
-        <v>1.0033</v>
-      </c>
+      <c r="P105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>CBWWDG2</t>
+          <t>ADPMH1</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr"/>
@@ -12580,7 +12580,9 @@
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="5" t="inlineStr"/>
       <c r="G106" s="5" t="inlineStr"/>
-      <c r="H106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="n">
+        <v>1.0055</v>
+      </c>
       <c r="I106" s="5" t="n">
         <v>1.0036</v>
       </c>
@@ -12751,11 +12753,11 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>STANV1</t>
+          <t>AMCORGR</t>
         </is>
       </c>
       <c r="B111" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0111</v>
       </c>
       <c r="C111" s="5" t="inlineStr"/>
       <c r="D111" s="5" t="inlineStr"/>
@@ -12799,11 +12801,11 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>TEATREE1</t>
+          <t>STANV1</t>
         </is>
       </c>
       <c r="B113" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="C113" s="5" t="inlineStr"/>
       <c r="D113" s="5" t="inlineStr"/>
@@ -12847,11 +12849,11 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>ANGAS1</t>
+          <t>TEATREE1</t>
         </is>
       </c>
       <c r="B115" s="5" t="n">
-        <v>1.0061</v>
+        <v>1.0042</v>
       </c>
       <c r="C115" s="5" t="inlineStr"/>
       <c r="D115" s="5" t="inlineStr"/>
@@ -12871,11 +12873,11 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>AMCORGR</t>
+          <t>ANGAS1</t>
         </is>
       </c>
       <c r="B116" s="5" t="n">
-        <v>1.0111</v>
+        <v>1.0061</v>
       </c>
       <c r="C116" s="5" t="inlineStr"/>
       <c r="D116" s="5" t="inlineStr"/>
@@ -12945,14 +12947,14 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>NPSNL2</t>
+          <t>NPS1</t>
         </is>
       </c>
       <c r="B119" s="5" t="n">
-        <v>1.0482</v>
+        <v>0.9826</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1.0791</v>
+        <v>1.0098</v>
       </c>
       <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="5" t="inlineStr"/>
@@ -12971,14 +12973,14 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>NPSNL1</t>
+          <t>NPS2</t>
         </is>
       </c>
       <c r="B120" s="5" t="n">
-        <v>0.9929</v>
+        <v>0.9826</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>1.0132</v>
+        <v>1.0098</v>
       </c>
       <c r="D120" s="5" t="inlineStr"/>
       <c r="E120" s="5" t="inlineStr"/>
@@ -12997,14 +12999,14 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>NPS1</t>
+          <t>NPSNL1</t>
         </is>
       </c>
       <c r="B121" s="5" t="n">
-        <v>0.9826</v>
+        <v>0.9929</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0132</v>
       </c>
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="5" t="inlineStr"/>
@@ -13023,14 +13025,14 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>NPS2</t>
+          <t>NPSNL2</t>
         </is>
       </c>
       <c r="B122" s="5" t="n">
-        <v>0.9826</v>
+        <v>1.0482</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>1.0098</v>
+        <v>1.0791</v>
       </c>
       <c r="D122" s="5" t="inlineStr"/>
       <c r="E122" s="5" t="inlineStr"/>
@@ -13049,17 +13051,17 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>PEDLER1</t>
+          <t>TERMSTOR</t>
         </is>
       </c>
       <c r="B123" s="5" t="n">
-        <v>1.0075</v>
+        <v>1.0042</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1.0051</v>
+        <v>1.0037</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>1.0047</v>
+        <v>1.0034</v>
       </c>
       <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="5" t="inlineStr"/>
@@ -13105,17 +13107,17 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>TERMSTOR</t>
+          <t>PEDLER1</t>
         </is>
       </c>
       <c r="B125" s="5" t="n">
-        <v>1.0042</v>
+        <v>1.0075</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>1.0037</v>
+        <v>1.0051</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>1.0034</v>
+        <v>1.0047</v>
       </c>
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="5" t="inlineStr"/>
@@ -13133,7 +13135,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>TORRA2</t>
+          <t>TORRA4</t>
         </is>
       </c>
       <c r="B126" s="5" t="n">
@@ -13167,7 +13169,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>TORRA4</t>
+          <t>TORRA2</t>
         </is>
       </c>
       <c r="B127" s="5" t="n">
@@ -13863,12 +13865,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS1</t>
+          <t>SMFBESS2</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 1</t>
+          <t>Summerfield BESS 2</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -13892,12 +13894,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>SMFBESS2</t>
+          <t>SMFBESS1</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Summerfield BESS 2</t>
+          <t>Summerfield BESS 1</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -14110,7 +14112,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>LADBROK1</t>
+          <t>LADBROK2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -14139,7 +14141,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>LADBROK2</t>
+          <t>LADBROK1</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -14284,12 +14286,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY1</t>
+          <t>LKBONNY3</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Wind Farm Stage 1</t>
+          <t>Lake Bonney Stage 3 Wind Farm</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -14342,12 +14344,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>LKBONNY3</t>
+          <t>LKBONNY1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Lake Bonney Stage 3 Wind Farm</t>
+          <t>Lake Bonney Wind Farm Stage 1</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -14487,7 +14489,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TB2SF1</t>
+          <t>TB2B1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -14497,7 +14499,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
@@ -14516,7 +14518,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TB2B1</t>
+          <t>TB2SF1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -14526,7 +14528,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
